--- a/Towers & Upgrades.xlsx
+++ b/Towers & Upgrades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\Programming\Python\Points TD 2\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA2C7D6-03F7-466E-9057-9870C19E95D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716E378-6A76-441A-93EB-51A406CB24B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -288,7 +288,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -7113,14 +7112,6 @@
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
       <c r="L32">
         <v>31</v>
       </c>
@@ -7154,15 +7145,7 @@
         <v>1.6294999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A33" s="15"/>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
+    <row r="33" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>32</v>
       </c>
@@ -7196,15 +7179,7 @@
         <v>1.7628000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A34" s="15"/>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+    <row r="34" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>33</v>
       </c>
@@ -7238,15 +7213,7 @@
         <v>1.9015000000000002</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
+    <row r="35" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>34</v>
       </c>
@@ -7280,15 +7247,7 @@
         <v>2.0456000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
+    <row r="36" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L36">
         <v>35</v>
       </c>
@@ -7322,7 +7281,7 @@
         <v>2.1951000000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L37">
         <v>36</v>
       </c>
@@ -7356,7 +7315,7 @@
         <v>2.3500000000000005</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L38">
         <v>37</v>
       </c>
@@ -7390,7 +7349,7 @@
         <v>2.5103000000000009</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L39">
         <v>38</v>
       </c>
@@ -7424,7 +7383,7 @@
         <v>2.6760000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L40">
         <v>39</v>
       </c>
@@ -7458,7 +7417,7 @@
         <v>2.8471000000000002</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L41">
         <v>40</v>
       </c>
@@ -7492,7 +7451,7 @@
         <v>3.0236000000000005</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L42">
         <v>41</v>
       </c>
@@ -7526,7 +7485,7 @@
         <v>3.2055000000000007</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L43">
         <v>42</v>
       </c>
@@ -7560,7 +7519,7 @@
         <v>3.3928000000000007</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L44">
         <v>43</v>
       </c>
@@ -7594,7 +7553,7 @@
         <v>3.5855000000000006</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L45">
         <v>44</v>
       </c>
@@ -7628,7 +7587,7 @@
         <v>3.7835999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L46">
         <v>45</v>
       </c>
@@ -7662,7 +7621,7 @@
         <v>3.9871000000000008</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L47">
         <v>46</v>
       </c>
@@ -7696,7 +7655,7 @@
         <v>4.1960000000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L48">
         <v>47</v>
       </c>

--- a/Towers & Upgrades.xlsx
+++ b/Towers & Upgrades.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\Programming\Python\Points TD 2\Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daten\Programmieren\Python\Eigene Projekte\Points TD 2\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0716E378-6A76-441A-93EB-51A406CB24B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD5B78E-549A-43E0-84F6-0C6EFC4687D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -290,7 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -318,7 +318,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -458,10 +458,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$Q$2:$Q$71</c:f>
+              <c:f>Tabelle1!$Q$2:$Q$81</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="80"/>
                 <c:pt idx="0">
                   <c:v>0.05</c:v>
                 </c:pt>
@@ -671,6 +671,36 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>10.753</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11.169</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>11.513</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>11.84</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>12.23</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>12.57</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>12.983000000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>13.37</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>13.769</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>14.113</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>14.502000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -810,6 +840,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -817,7 +848,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -855,7 +885,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1008,10 +1038,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$P$2:$P$71</c:f>
+              <c:f>Tabelle1!$P$2:$P$81</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="80"/>
                 <c:pt idx="0">
                   <c:v>0.14899999999999999</c:v>
                 </c:pt>
@@ -1221,6 +1251,36 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>1.9350000000000001</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2.4649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.875</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2.1579999999999999</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1.9059999999999999</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1.774</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2.1019999999999999</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2.331</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2.2549999999999999</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2.339</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3.3730000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1264,10 +1324,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$R$2:$R$71</c:f>
+              <c:f>Tabelle1!$R$2:$R$81</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="80"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -1477,6 +1537,36 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>0.18</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>0.221</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>0.16300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>0.156</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>0.14099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>0.16200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>0.17399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>0.16400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>0.16600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>0.23300000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1505,10 +1595,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$S$2:$S$71</c:f>
+              <c:f>Tabelle1!$S$2:$S$81</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="70"/>
+                <c:ptCount val="80"/>
                 <c:pt idx="0">
                   <c:v>2.110766511004619</c:v>
                 </c:pt>
@@ -1718,6 +1808,36 @@
                 </c:pt>
                 <c:pt idx="69">
                   <c:v>2.7371875400769583</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2.5095867012298205</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2.0044593143431828</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2.6772524679091445</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2.0678622777677655</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>1.8696893055930364</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2.2934801446750361</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2.1195379206428928</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2.5208683739455462</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2.5001858114388091</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>3.1455868373806295</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1857,6 +1977,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1864,7 +1985,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1902,7 +2022,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2304,6 +2424,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2311,7 +2432,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2349,7 +2469,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="de-DE"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2715,6 +2835,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2722,7 +2843,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -5140,8 +5260,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}" name="Waves" displayName="Waves" ref="L1:S71" totalsRowShown="0">
-  <autoFilter ref="L1:S71" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}" name="Waves" displayName="Waves" ref="L1:S81" totalsRowShown="0">
+  <autoFilter ref="L1:S81" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{C596E476-F34D-48B8-BAB6-31EDA5A2D2AB}" name="Wave"/>
     <tableColumn id="2" xr3:uid="{658BD531-EA5F-4C0A-AC63-7FBA171C7055}" name="Time"/>
@@ -5449,20 +5569,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:U81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.44140625" customWidth="1"/>
-    <col min="19" max="19" width="10.33203125" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" customWidth="1"/>
+    <col min="19" max="19" width="10.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -5515,7 +5635,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -5577,7 +5697,7 @@
         <v>0.14150000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -5641,7 +5761,7 @@
         <v>0.11280000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -5703,7 +5823,7 @@
         <v>8.950000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
@@ -5765,7 +5885,7 @@
         <v>7.1600000000000011E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
@@ -5829,7 +5949,7 @@
         <v>5.9100000000000014E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
@@ -5891,7 +6011,7 @@
         <v>5.2000000000000018E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -5953,7 +6073,7 @@
         <v>5.0300000000000011E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>37</v>
       </c>
@@ -6015,7 +6135,7 @@
         <v>5.400000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L10">
         <v>9</v>
       </c>
@@ -6049,7 +6169,7 @@
         <v>6.3100000000000017E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -6086,7 +6206,7 @@
         <v>7.760000000000003E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -6147,7 +6267,7 @@
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>0</v>
       </c>
@@ -6209,7 +6329,7 @@
         <v>0.12280000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
         <v>1</v>
       </c>
@@ -6273,7 +6393,7 @@
         <v>0.15350000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
         <v>2</v>
       </c>
@@ -6335,7 +6455,7 @@
         <v>0.18960000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>3</v>
       </c>
@@ -6398,7 +6518,7 @@
         <v>0.2311</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>4</v>
       </c>
@@ -6462,7 +6582,7 @@
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>5</v>
       </c>
@@ -6524,7 +6644,7 @@
         <v>0.33030000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>35</v>
       </c>
@@ -6586,7 +6706,7 @@
         <v>0.38800000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>37</v>
       </c>
@@ -6648,7 +6768,7 @@
         <v>0.45109999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L21">
         <v>20</v>
       </c>
@@ -6682,7 +6802,7 @@
         <v>0.51960000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L22">
         <v>21</v>
       </c>
@@ -6716,7 +6836,7 @@
         <v>0.59350000000000014</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L23">
         <v>22</v>
       </c>
@@ -6750,7 +6870,7 @@
         <v>0.67279999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>26</v>
       </c>
@@ -6799,7 +6919,7 @@
         <v>0.75750000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -6852,7 +6972,7 @@
         <v>0.84760000000000013</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -6899,7 +7019,7 @@
         <v>0.94310000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -6946,7 +7066,7 @@
         <v>1.0440000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -6993,7 +7113,7 @@
         <v>1.1503000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -7043,7 +7163,7 @@
         <v>1.262</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L30">
         <v>29</v>
       </c>
@@ -7077,7 +7197,7 @@
         <v>1.3791000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L31">
         <v>30</v>
       </c>
@@ -7111,7 +7231,7 @@
         <v>1.5016</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="L32">
         <v>31</v>
       </c>
@@ -7145,7 +7265,7 @@
         <v>1.6294999999999999</v>
       </c>
     </row>
-    <row r="33" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L33">
         <v>32</v>
       </c>
@@ -7179,7 +7299,7 @@
         <v>1.7628000000000001</v>
       </c>
     </row>
-    <row r="34" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L34">
         <v>33</v>
       </c>
@@ -7213,7 +7333,7 @@
         <v>1.9015000000000002</v>
       </c>
     </row>
-    <row r="35" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L35">
         <v>34</v>
       </c>
@@ -7247,7 +7367,7 @@
         <v>2.0456000000000003</v>
       </c>
     </row>
-    <row r="36" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L36">
         <v>35</v>
       </c>
@@ -7281,7 +7401,7 @@
         <v>2.1951000000000001</v>
       </c>
     </row>
-    <row r="37" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L37">
         <v>36</v>
       </c>
@@ -7315,7 +7435,7 @@
         <v>2.3500000000000005</v>
       </c>
     </row>
-    <row r="38" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L38">
         <v>37</v>
       </c>
@@ -7349,7 +7469,7 @@
         <v>2.5103000000000009</v>
       </c>
     </row>
-    <row r="39" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L39">
         <v>38</v>
       </c>
@@ -7383,7 +7503,7 @@
         <v>2.6760000000000002</v>
       </c>
     </row>
-    <row r="40" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L40">
         <v>39</v>
       </c>
@@ -7417,7 +7537,7 @@
         <v>2.8471000000000002</v>
       </c>
     </row>
-    <row r="41" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L41">
         <v>40</v>
       </c>
@@ -7451,7 +7571,7 @@
         <v>3.0236000000000005</v>
       </c>
     </row>
-    <row r="42" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="42" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L42">
         <v>41</v>
       </c>
@@ -7485,7 +7605,7 @@
         <v>3.2055000000000007</v>
       </c>
     </row>
-    <row r="43" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="43" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L43">
         <v>42</v>
       </c>
@@ -7519,7 +7639,7 @@
         <v>3.3928000000000007</v>
       </c>
     </row>
-    <row r="44" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="44" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L44">
         <v>43</v>
       </c>
@@ -7553,7 +7673,7 @@
         <v>3.5855000000000006</v>
       </c>
     </row>
-    <row r="45" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="45" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L45">
         <v>44</v>
       </c>
@@ -7587,7 +7707,7 @@
         <v>3.7835999999999999</v>
       </c>
     </row>
-    <row r="46" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="46" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L46">
         <v>45</v>
       </c>
@@ -7621,7 +7741,7 @@
         <v>3.9871000000000008</v>
       </c>
     </row>
-    <row r="47" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="47" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L47">
         <v>46</v>
       </c>
@@ -7655,7 +7775,7 @@
         <v>4.1960000000000006</v>
       </c>
     </row>
-    <row r="48" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="48" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L48">
         <v>47</v>
       </c>
@@ -7689,7 +7809,7 @@
         <v>4.4103000000000003</v>
       </c>
     </row>
-    <row r="49" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="49" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L49">
         <v>48</v>
       </c>
@@ -7723,7 +7843,7 @@
         <v>4.6300000000000008</v>
       </c>
     </row>
-    <row r="50" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="50" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L50">
         <v>49</v>
       </c>
@@ -7757,7 +7877,7 @@
         <v>4.8551000000000011</v>
       </c>
     </row>
-    <row r="51" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="51" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L51">
         <v>50</v>
       </c>
@@ -7791,7 +7911,7 @@
         <v>5.0856000000000003</v>
       </c>
     </row>
-    <row r="52" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="52" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L52">
         <v>51</v>
       </c>
@@ -7825,7 +7945,7 @@
         <v>5.3215000000000003</v>
       </c>
     </row>
-    <row r="53" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="53" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L53">
         <v>52</v>
       </c>
@@ -7859,7 +7979,7 @@
         <v>5.5628000000000011</v>
       </c>
     </row>
-    <row r="54" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="54" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L54">
         <v>53</v>
       </c>
@@ -7893,7 +8013,7 @@
         <v>5.8095000000000008</v>
       </c>
     </row>
-    <row r="55" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="55" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L55">
         <v>54</v>
       </c>
@@ -7927,7 +8047,7 @@
         <v>6.0616000000000012</v>
       </c>
     </row>
-    <row r="56" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="56" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L56">
         <v>55</v>
       </c>
@@ -7961,7 +8081,7 @@
         <v>6.3191000000000006</v>
       </c>
     </row>
-    <row r="57" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="57" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L57">
         <v>56</v>
       </c>
@@ -7995,7 +8115,7 @@
         <v>6.5819999999999999</v>
       </c>
     </row>
-    <row r="58" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="58" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L58">
         <v>57</v>
       </c>
@@ -8029,7 +8149,7 @@
         <v>6.8503000000000016</v>
       </c>
     </row>
-    <row r="59" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="59" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L59">
         <v>58</v>
       </c>
@@ -8063,7 +8183,7 @@
         <v>7.1240000000000014</v>
       </c>
     </row>
-    <row r="60" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="60" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L60">
         <v>59</v>
       </c>
@@ -8097,7 +8217,7 @@
         <v>7.4031000000000002</v>
       </c>
     </row>
-    <row r="61" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="61" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L61">
         <v>60</v>
       </c>
@@ -8131,7 +8251,7 @@
         <v>7.6876000000000007</v>
       </c>
     </row>
-    <row r="62" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="62" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L62">
         <v>61</v>
       </c>
@@ -8165,7 +8285,7 @@
         <v>7.9775000000000018</v>
       </c>
     </row>
-    <row r="63" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="63" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L63">
         <v>62</v>
       </c>
@@ -8199,7 +8319,7 @@
         <v>8.2728000000000002</v>
       </c>
     </row>
-    <row r="64" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="64" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L64">
         <v>63</v>
       </c>
@@ -8233,7 +8353,7 @@
         <v>8.5734999999999992</v>
       </c>
     </row>
-    <row r="65" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="65" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L65">
         <v>64</v>
       </c>
@@ -8267,7 +8387,7 @@
         <v>8.8795999999999999</v>
       </c>
     </row>
-    <row r="66" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="66" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L66">
         <v>65</v>
       </c>
@@ -8301,7 +8421,7 @@
         <v>9.1911000000000005</v>
       </c>
     </row>
-    <row r="67" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="67" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L67">
         <v>66</v>
       </c>
@@ -8335,7 +8455,7 @@
         <v>9.5079999999999991</v>
       </c>
     </row>
-    <row r="68" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="68" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L68">
         <v>67</v>
       </c>
@@ -8369,7 +8489,7 @@
         <v>9.8302999999999994</v>
       </c>
     </row>
-    <row r="69" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="69" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L69">
         <v>68</v>
       </c>
@@ -8403,7 +8523,7 @@
         <v>10.157999999999999</v>
       </c>
     </row>
-    <row r="70" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="70" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L70">
         <v>69</v>
       </c>
@@ -8437,7 +8557,7 @@
         <v>10.491099999999999</v>
       </c>
     </row>
-    <row r="71" spans="12:21" x14ac:dyDescent="0.3">
+    <row r="71" spans="12:21" x14ac:dyDescent="0.25">
       <c r="L71">
         <v>70</v>
       </c>
@@ -8469,6 +8589,346 @@
       <c r="U71">
         <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
         <v>10.829599999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L72">
+        <v>71</v>
+      </c>
+      <c r="M72">
+        <v>864</v>
+      </c>
+      <c r="N72">
+        <v>2130</v>
+      </c>
+      <c r="O72">
+        <v>9650</v>
+      </c>
+      <c r="P72">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.4649999999999999</v>
+      </c>
+      <c r="Q72" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>11.169</v>
+      </c>
+      <c r="R72">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.221</v>
+      </c>
+      <c r="S72" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.5095867012298205</v>
+      </c>
+      <c r="U72">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>11.173500000000001</v>
+      </c>
+    </row>
+    <row r="73" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L73">
+        <v>72</v>
+      </c>
+      <c r="M73">
+        <v>760</v>
+      </c>
+      <c r="N73">
+        <v>1425</v>
+      </c>
+      <c r="O73">
+        <v>8750</v>
+      </c>
+      <c r="P73">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>1.875</v>
+      </c>
+      <c r="Q73" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>11.513</v>
+      </c>
+      <c r="R73">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.16300000000000001</v>
+      </c>
+      <c r="S73" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.0044593143431828</v>
+      </c>
+      <c r="U73">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>11.5228</v>
+      </c>
+    </row>
+    <row r="74" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L74">
+        <v>73</v>
+      </c>
+      <c r="M74">
+        <v>549</v>
+      </c>
+      <c r="N74">
+        <v>1185</v>
+      </c>
+      <c r="O74">
+        <v>6500</v>
+      </c>
+      <c r="P74">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.1579999999999999</v>
+      </c>
+      <c r="Q74" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>11.84</v>
+      </c>
+      <c r="R74">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.182</v>
+      </c>
+      <c r="S74" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.6772524679091445</v>
+      </c>
+      <c r="U74">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>11.877500000000001</v>
+      </c>
+    </row>
+    <row r="75" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L75">
+        <v>74</v>
+      </c>
+      <c r="M75">
+        <v>695</v>
+      </c>
+      <c r="N75">
+        <v>1325</v>
+      </c>
+      <c r="O75">
+        <v>8500</v>
+      </c>
+      <c r="P75">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>1.9059999999999999</v>
+      </c>
+      <c r="Q75" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>12.23</v>
+      </c>
+      <c r="R75">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.156</v>
+      </c>
+      <c r="S75" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.0678622777677655</v>
+      </c>
+      <c r="U75">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>12.2376</v>
+      </c>
+    </row>
+    <row r="76" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L76">
+        <v>75</v>
+      </c>
+      <c r="M76">
+        <v>716</v>
+      </c>
+      <c r="N76">
+        <v>1270</v>
+      </c>
+      <c r="O76">
+        <v>9000</v>
+      </c>
+      <c r="P76">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>1.774</v>
+      </c>
+      <c r="Q76" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>12.57</v>
+      </c>
+      <c r="R76">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.14099999999999999</v>
+      </c>
+      <c r="S76" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>1.8696893055930364</v>
+      </c>
+      <c r="U76">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>12.6031</v>
+      </c>
+    </row>
+    <row r="77" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L77">
+        <v>76</v>
+      </c>
+      <c r="M77">
+        <v>647</v>
+      </c>
+      <c r="N77">
+        <v>1360</v>
+      </c>
+      <c r="O77">
+        <v>8400</v>
+      </c>
+      <c r="P77">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.1019999999999999</v>
+      </c>
+      <c r="Q77" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>12.983000000000001</v>
+      </c>
+      <c r="R77">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.16200000000000001</v>
+      </c>
+      <c r="S77" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.2934801446750361</v>
+      </c>
+      <c r="U77">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>12.974</v>
+      </c>
+    </row>
+    <row r="78" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L78">
+        <v>77</v>
+      </c>
+      <c r="M78">
+        <v>905</v>
+      </c>
+      <c r="N78">
+        <v>2110</v>
+      </c>
+      <c r="O78">
+        <v>12100</v>
+      </c>
+      <c r="P78">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.331</v>
+      </c>
+      <c r="Q78" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>13.37</v>
+      </c>
+      <c r="R78">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="S78" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.1195379206428928</v>
+      </c>
+      <c r="U78">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>13.350300000000001</v>
+      </c>
+    </row>
+    <row r="79" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L79">
+        <v>78</v>
+      </c>
+      <c r="M79">
+        <v>581</v>
+      </c>
+      <c r="N79">
+        <v>1310</v>
+      </c>
+      <c r="O79">
+        <v>8000</v>
+      </c>
+      <c r="P79">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.2549999999999999</v>
+      </c>
+      <c r="Q79" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>13.769</v>
+      </c>
+      <c r="R79">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.16400000000000001</v>
+      </c>
+      <c r="S79" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.5208683739455462</v>
+      </c>
+      <c r="U79">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>13.731999999999999</v>
+      </c>
+    </row>
+    <row r="80" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L80">
+        <v>79</v>
+      </c>
+      <c r="M80">
+        <v>620</v>
+      </c>
+      <c r="N80">
+        <v>1450</v>
+      </c>
+      <c r="O80">
+        <v>8750</v>
+      </c>
+      <c r="P80">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>2.339</v>
+      </c>
+      <c r="Q80" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>14.113</v>
+      </c>
+      <c r="R80">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.16600000000000001</v>
+      </c>
+      <c r="S80" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>2.5001858114388091</v>
+      </c>
+      <c r="U80">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>14.1191</v>
+      </c>
+    </row>
+    <row r="81" spans="12:21" x14ac:dyDescent="0.25">
+      <c r="L81">
+        <v>80</v>
+      </c>
+      <c r="M81">
+        <v>793</v>
+      </c>
+      <c r="N81">
+        <v>2675</v>
+      </c>
+      <c r="O81">
+        <v>11500</v>
+      </c>
+      <c r="P81">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <v>3.3730000000000002</v>
+      </c>
+      <c r="Q81" s="4">
+        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <v>14.502000000000001</v>
+      </c>
+      <c r="R81">
+        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="S81" s="5">
+        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <v>3.1455868373806295</v>
+      </c>
+      <c r="U81">
+        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <v>14.511600000000001</v>
       </c>
     </row>
   </sheetData>
@@ -8517,18 +8977,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2611AF0A-4669-45BC-A52D-B98A4F110345}">
   <dimension ref="A1:AJ41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.44140625" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -8572,7 +9032,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8625,7 +9085,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -8678,7 +9138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -8731,7 +9191,7 @@
         <v>1.806</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -8784,7 +9244,7 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -8837,7 +9297,7 @@
         <v>1.585</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -8898,7 +9358,7 @@
       <c r="AI7" s="7"/>
       <c r="AJ7" s="9"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L8">
         <v>7</v>
       </c>
@@ -8932,7 +9392,7 @@
       <c r="AI8" s="7"/>
       <c r="AJ8" s="9"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L9">
         <v>8</v>
       </c>
@@ -8966,7 +9426,7 @@
       <c r="AI9" s="7"/>
       <c r="AJ9" s="9"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
       <c r="L10">
         <v>9</v>
       </c>
@@ -9000,7 +9460,7 @@
       <c r="AI10" s="7"/>
       <c r="AJ10" s="9"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -9037,7 +9497,7 @@
       <c r="AI11" s="7"/>
       <c r="AJ11" s="9"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -9095,7 +9555,7 @@
       <c r="AI12" s="7"/>
       <c r="AJ12" s="9"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -9156,7 +9616,7 @@
       <c r="AI13" s="7"/>
       <c r="AJ13" s="9"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -9217,7 +9677,7 @@
       <c r="AI14" s="7"/>
       <c r="AJ14" s="9"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -9278,7 +9738,7 @@
       <c r="AI15" s="7"/>
       <c r="AJ15" s="9"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -9340,7 +9800,7 @@
       <c r="AI16" s="7"/>
       <c r="AJ16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -9393,7 +9853,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -9446,7 +9906,7 @@
         <v>1.238</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L19">
         <v>18</v>
       </c>
@@ -9472,7 +9932,7 @@
         <v>1.321</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L20">
         <v>19</v>
       </c>
@@ -9498,7 +9958,7 @@
         <v>1.145</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L21">
         <v>20</v>
       </c>
@@ -9524,7 +9984,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L22">
         <v>21</v>
       </c>
@@ -9550,7 +10010,7 @@
         <v>1.083</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L23">
         <v>22</v>
       </c>
@@ -9576,7 +10036,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L24">
         <v>23</v>
       </c>
@@ -9602,7 +10062,7 @@
         <v>0.97599999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L25">
         <v>24</v>
       </c>
@@ -9628,7 +10088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L26">
         <v>25</v>
       </c>
@@ -9654,7 +10114,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L27">
         <v>26</v>
       </c>
@@ -9680,7 +10140,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L28">
         <v>27</v>
       </c>
@@ -9706,7 +10166,7 @@
         <v>0.78800000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L29">
         <v>28</v>
       </c>
@@ -9732,7 +10192,7 @@
         <v>0.69799999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L30">
         <v>29</v>
       </c>
@@ -9758,7 +10218,7 @@
         <v>0.76700000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L31">
         <v>30</v>
       </c>
@@ -9784,7 +10244,7 @@
         <v>0.68500000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="L32">
         <v>31</v>
       </c>
@@ -9810,7 +10270,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L33">
         <v>32</v>
       </c>
@@ -9836,7 +10296,7 @@
         <v>0.65600000000000003</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L34">
         <v>33</v>
       </c>
@@ -9862,7 +10322,7 @@
         <v>0.69699999999999995</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L35">
         <v>34</v>
       </c>
@@ -9888,7 +10348,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L36">
         <v>35</v>
       </c>
@@ -9914,7 +10374,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L37">
         <v>36</v>
       </c>
@@ -9940,7 +10400,7 @@
         <v>0.35599999999999998</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L38">
         <v>37</v>
       </c>
@@ -9966,7 +10426,7 @@
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L39">
         <v>38</v>
       </c>
@@ -9992,7 +10452,7 @@
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L40">
         <v>39</v>
       </c>
@@ -10018,7 +10478,7 @@
         <v>0.38900000000000001</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.25">
       <c r="L41">
         <v>40</v>
       </c>

--- a/Towers & Upgrades.xlsx
+++ b/Towers & Upgrades.xlsx
@@ -5,16 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Daten\Programmieren\Python\Eigene Projekte\Points TD 2\Program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\Programming\Python\Points TD 2\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD5B78E-549A-43E0-84F6-0C6EFC4687D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9792A9-F45E-4A2D-B58D-326E3919926C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Alte Kopie" sheetId="2" r:id="rId2"/>
+    <sheet name="Current" sheetId="3" r:id="rId1"/>
+    <sheet name="Old Copy" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="50">
   <si>
     <t>Ninja</t>
   </si>
@@ -160,6 +160,33 @@
   </si>
   <si>
     <t>=1.0 - 1.2</t>
+  </si>
+  <si>
+    <t>Master Upgrades</t>
+  </si>
+  <si>
+    <t>Ninja DoubleKill</t>
+  </si>
+  <si>
+    <t>Ninja Robot</t>
+  </si>
+  <si>
+    <t>Bomber BiggerRange</t>
+  </si>
+  <si>
+    <t>Bomber AtomicBomb</t>
+  </si>
+  <si>
+    <t>Machine Ray</t>
+  </si>
+  <si>
+    <t>Machine Hot</t>
+  </si>
+  <si>
+    <t>Sniper Sharper+</t>
+  </si>
+  <si>
+    <t>Sniper fast</t>
   </si>
 </sst>
 </file>
@@ -290,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -318,7 +345,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -458,10 +485,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$Q$2:$Q$81</c:f>
+              <c:f>Current!$Q$2:$Q$86</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="80"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
                   <c:v>0.05</c:v>
                 </c:pt>
@@ -493,13 +520,13 @@
                   <c:v>0.124</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.13900000000000001</c:v>
+                  <c:v>0.13800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.153</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.17100000000000001</c:v>
+                  <c:v>0.17199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.19900000000000001</c:v>
@@ -553,28 +580,28 @@
                   <c:v>1.5629999999999999</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.6240000000000001</c:v>
+                  <c:v>1.629</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>1.776</c:v>
+                  <c:v>1.774</c:v>
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>1.905</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>2.0649999999999999</c:v>
+                  <c:v>2.06</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.1819999999999999</c:v>
+                  <c:v>2.1789999999999998</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>2.3119999999999998</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.5129999999999999</c:v>
+                  <c:v>2.5049999999999999</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.6629999999999998</c:v>
+                  <c:v>2.6539999999999999</c:v>
                 </c:pt>
                 <c:pt idx="38">
                   <c:v>2.84</c:v>
@@ -701,6 +728,21 @@
                 </c:pt>
                 <c:pt idx="79">
                   <c:v>14.502000000000001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>14.907</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>15.385</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>15.714</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>16.129000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>16.574999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -708,7 +750,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6E97-42C1-B1AC-EF6AF65BCF56}"/>
+              <c16:uniqueId val="{00000001-025E-4FA3-AC7F-2A1732829B68}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -885,7 +927,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1038,10 +1080,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$P$2:$P$81</c:f>
+              <c:f>Current!$P$2:$P$86</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="80"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
                   <c:v>0.14899999999999999</c:v>
                 </c:pt>
@@ -1070,52 +1112,52 @@
                   <c:v>0.22600000000000001</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.22800000000000001</c:v>
+                  <c:v>0.40699999999999997</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>0.254</c:v>
+                  <c:v>0.47199999999999998</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>0.28000000000000003</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.28599999999999998</c:v>
+                  <c:v>0.49</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>0.33100000000000002</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.36299999999999999</c:v>
+                  <c:v>0.45900000000000002</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0.38800000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.41099999999999998</c:v>
+                  <c:v>0.73499999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.48199999999999998</c:v>
+                  <c:v>0.66300000000000003</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.53300000000000003</c:v>
+                  <c:v>0.68700000000000006</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.55300000000000005</c:v>
+                  <c:v>0.74199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>0.60699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.56499999999999995</c:v>
+                  <c:v>0.91100000000000003</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.66300000000000003</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.69399999999999995</c:v>
+                  <c:v>1.125</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.78100000000000003</c:v>
+                  <c:v>0.95699999999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.86299999999999999</c:v>
@@ -1133,31 +1175,31 @@
                   <c:v>1.359</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.74099999999999999</c:v>
+                  <c:v>1.3089999999999999</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.93200000000000005</c:v>
+                  <c:v>1.371</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.88900000000000001</c:v>
+                  <c:v>1.28</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.79500000000000004</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.018</c:v>
+                  <c:v>1.913</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>1.272</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.216</c:v>
+                  <c:v>1.7689999999999999</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.288</c:v>
+                  <c:v>1.885</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.97</c:v>
+                  <c:v>2.2839999999999998</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>1.5940000000000001</c:v>
@@ -1281,6 +1323,21 @@
                 </c:pt>
                 <c:pt idx="79">
                   <c:v>3.3730000000000002</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2.36</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2.4180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.714</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2.129</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2.597</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1288,7 +1345,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8EB4-4A67-9826-953417BD37A9}"/>
+              <c16:uniqueId val="{00000001-1ECE-4375-B1BF-FECCE14D03A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1324,10 +1381,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$R$2:$R$81</c:f>
+              <c:f>Current!$R$2:$R$86</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="80"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -1356,52 +1413,52 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.833</c:v>
+                  <c:v>3.2730000000000001</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.833</c:v>
+                  <c:v>3.407</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>1.833</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.667</c:v>
+                  <c:v>2.8570000000000002</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1.667</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.5409999999999999</c:v>
+                  <c:v>1.946</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>1.4550000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>1.357</c:v>
+                  <c:v>2.4289999999999998</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>1.333</c:v>
+                  <c:v>1.833</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>1.238</c:v>
+                  <c:v>1.595</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>1.1000000000000001</c:v>
+                  <c:v>1.4750000000000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>1.0740000000000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.91500000000000004</c:v>
+                  <c:v>1.4750000000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>0.92300000000000004</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.85599999999999998</c:v>
+                  <c:v>1.389</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.86899999999999999</c:v>
+                  <c:v>1.0649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>0.86299999999999999</c:v>
@@ -1419,31 +1476,31 @@
                   <c:v>0.87</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.45600000000000002</c:v>
+                  <c:v>0.80300000000000005</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.52500000000000002</c:v>
+                  <c:v>0.77300000000000002</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.46700000000000003</c:v>
+                  <c:v>0.67200000000000004</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.38500000000000001</c:v>
+                  <c:v>0.60699999999999998</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>0.46700000000000003</c:v>
+                  <c:v>0.878</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>0.55000000000000004</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>0.48399999999999999</c:v>
+                  <c:v>0.70599999999999996</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>0.48399999999999999</c:v>
+                  <c:v>0.71</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>0.34200000000000003</c:v>
+                  <c:v>0.80400000000000005</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>0.52800000000000002</c:v>
@@ -1567,6 +1624,21 @@
                 </c:pt>
                 <c:pt idx="79">
                   <c:v>0.23300000000000001</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>0.158</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>0.109</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>0.157</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1574,7 +1646,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D94F-4B78-AA03-13F1014B78E9}"/>
+              <c16:uniqueId val="{00000003-1ECE-4375-B1BF-FECCE14D03A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1595,10 +1667,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Tabelle1!$S$2:$S$81</c:f>
+              <c:f>Current!$S$2:$S$86</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="80"/>
+                <c:ptCount val="85"/>
                 <c:pt idx="0">
                   <c:v>2.110766511004619</c:v>
                 </c:pt>
@@ -1627,52 +1699,52 @@
                   <c:v>2.2598870056497176</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.081156522472134</c:v>
+                  <c:v>3.8784918884566468</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.3217526522376981</c:v>
+                  <c:v>4.0605637361946707</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2.558364387497591</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.3328473740792175</c:v>
+                  <c:v>3.7055340491100708</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2.7036310626745901</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>2.6692505388119132</c:v>
+                  <c:v>3.3716848911308377</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2.6150782544028783</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>2.4550641705247003</c:v>
+                  <c:v>4.3932727262020954</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.7824109358536178</c:v>
+                  <c:v>3.8258150367987249</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>2.6024001945294217</c:v>
+                  <c:v>3.3530925583359856</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>2.767295597484277</c:v>
+                  <c:v>3.7106918238993711</c:v>
                 </c:pt>
                 <c:pt idx="20">
                   <c:v>2.6135315192557318</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>2.3279003328796541</c:v>
+                  <c:v>3.7505060918616642</c:v>
                 </c:pt>
                 <c:pt idx="22">
                   <c:v>2.6004349410587939</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>2.7876435532498487</c:v>
+                  <c:v>4.5200773999022976</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>2.6938388145450194</c:v>
+                  <c:v>3.3027201904353323</c:v>
                 </c:pt>
                 <c:pt idx="25">
                   <c:v>3.049397993866986</c:v>
@@ -1690,31 +1762,31 @@
                   <c:v>3.5098911575004714</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>1.8527918781725889</c:v>
+                  <c:v>3.2713849287169041</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.4146359263287054</c:v>
+                  <c:v>3.5528760696057584</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.0951312035156961</c:v>
+                  <c:v>3.0179866145880863</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>1.9870967741935481</c:v>
+                  <c:v>3.0765189131164057</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>2.3998775603907063</c:v>
+                  <c:v>4.5085904530861383</c:v>
                 </c:pt>
                 <c:pt idx="35">
                   <c:v>2.8435546534679408</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>2.4321608040201004</c:v>
+                  <c:v>3.5370741482965937</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>2.6022407941181953</c:v>
+                  <c:v>3.80859247566814</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.9808496933749566</c:v>
+                  <c:v>4.6622437905044718</c:v>
                 </c:pt>
                 <c:pt idx="39">
                   <c:v>2.9595194521967643</c:v>
@@ -1838,6 +1910,21 @@
                 </c:pt>
                 <c:pt idx="79">
                   <c:v>3.1455868373806295</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2.1546021930845041</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2.8895636709183137</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1.6345072958495868</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1.904264342128853</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2.1201844919117745</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1845,7 +1932,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D94F-4B78-AA03-13F1014B78E9}"/>
+              <c16:uniqueId val="{00000004-1ECE-4375-B1BF-FECCE14D03A7}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2022,7 +2109,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2162,7 +2249,7 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>'Alte Kopie'!$Q$2:$Q$42</c:f>
+              <c:f>'Old Copy'!$Q$2:$Q$42</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="41"/>
@@ -2469,7 +2556,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="de-DE"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2573,7 +2660,7 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>'Alte Kopie'!$P$2:$P$42</c:f>
+              <c:f>'Old Copy'!$P$2:$P$42</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="41"/>
@@ -5118,14 +5205,16 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Diagramm 4">
+        <xdr:cNvPr id="2" name="Diagramm 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{76E71ABD-1979-FA64-C6AE-E1C5EA42880E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{254EBE1F-9CB0-4A36-80E3-D6792F1F1C89}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5154,14 +5243,16 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="7" name="Diagramm 6">
+        <xdr:cNvPr id="3" name="Diagramm 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEB38043-6169-5D09-B773-CF53C42CFE9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA87C06C-EB0B-4F9E-99CC-ABF4F2F3B4D3}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -5260,24 +5351,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}" name="Waves" displayName="Waves" ref="L1:S81" totalsRowShown="0">
-  <autoFilter ref="L1:S81" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D17B983-4C4E-4251-9CC2-79B2CFAB8B8A}" name="Waves4" displayName="Waves4" ref="L1:S86" totalsRowShown="0">
+  <autoFilter ref="L1:S86" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{C596E476-F34D-48B8-BAB6-31EDA5A2D2AB}" name="Wave"/>
-    <tableColumn id="2" xr3:uid="{658BD531-EA5F-4C0A-AC63-7FBA171C7055}" name="Time"/>
-    <tableColumn id="3" xr3:uid="{9CF65F60-CD90-44C6-91FC-26B3B481B8DC}" name="Money"/>
-    <tableColumn id="4" xr3:uid="{9BE76415-D71A-4D7A-B911-588FF8B333A1}" name="Health"/>
-    <tableColumn id="5" xr3:uid="{7B3573DF-37A3-4ACC-BB7E-48E3715E80A2}" name="M / T">
-      <calculatedColumnFormula>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{154764AE-2BF6-4E60-A3EE-81C43EB3C9DC}" name="Wave"/>
+    <tableColumn id="2" xr3:uid="{8A43BFD4-098B-4841-A8D7-3E1888255D8F}" name="Time"/>
+    <tableColumn id="3" xr3:uid="{9DACF8C6-24EC-4E33-A20E-BD3D86A60C60}" name="Money"/>
+    <tableColumn id="4" xr3:uid="{AA4489B8-2B01-4799-B1E2-6FED07D60CD9}" name="Health"/>
+    <tableColumn id="5" xr3:uid="{F6B07731-B180-4EDA-97F0-F28ED97FC1A4}" name="M / T">
+      <calculatedColumnFormula>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{91E23E5A-F67D-4CEA-B1CF-58626B21BBB0}" name="H / T" dataDxfId="2">
-      <calculatedColumnFormula>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{FDEDEE5F-2E38-49D5-A0C2-D94173FDBDAF}" name="H / T" dataDxfId="2">
+      <calculatedColumnFormula>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3A3EA08A-5B7D-4363-B7B6-F3EEA8916E91}" name="M / H">
-      <calculatedColumnFormula>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{FED1585E-32FC-4823-8B5F-1F7D02430A8C}" name="M / H">
+      <calculatedColumnFormula>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{7E68E024-47D5-4ECA-9534-8FAC2F31D088}" name="M/TH" dataDxfId="1">
-      <calculatedColumnFormula>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</calculatedColumnFormula>
+    <tableColumn id="8" xr3:uid="{71F8F601-3F0B-414E-BA77-E99C73F8743C}" name="M/TH" dataDxfId="1">
+      <calculatedColumnFormula>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -5568,21 +5659,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U81"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E183A86B-E41F-4C03-888F-921AD8D0823F}">
+  <dimension ref="A1:U86"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" customWidth="1"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" customWidth="1"/>
+    <col min="19" max="19" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -5635,7 +5726,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>0</v>
       </c>
@@ -5656,11 +5747,11 @@
         <v>280</v>
       </c>
       <c r="G2">
-        <f>100/C2*B2*E2</f>
+        <f>100/C2*B2</f>
         <v>4.5454545454545459</v>
       </c>
       <c r="H2" s="2">
-        <f>G2*100/F2</f>
+        <f>G2*100*E2/F2</f>
         <v>1.6233766233766234</v>
       </c>
       <c r="I2" s="10"/>
@@ -5677,27 +5768,27 @@
         <v>50</v>
       </c>
       <c r="P2">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.14899999999999999</v>
       </c>
       <c r="Q2" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.05</v>
       </c>
       <c r="R2">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>3</v>
       </c>
       <c r="S2" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.110766511004619</v>
       </c>
       <c r="U2">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.14150000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
@@ -5718,11 +5809,11 @@
         <v>680</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G7" si="1">100/C3*B3*E3</f>
-        <v>10.857142857142856</v>
+        <f t="shared" ref="G3:G9" si="1">100/C3*B3</f>
+        <v>4.7619047619047619</v>
       </c>
       <c r="H3" s="2">
-        <f t="shared" ref="H3:H7" si="2">G3*100/F3</f>
+        <f t="shared" ref="H3:H9" si="2">G3*100*E3/F3</f>
         <v>1.5966386554621845</v>
       </c>
       <c r="I3" s="11" t="s">
@@ -5741,27 +5832,27 @@
         <v>50</v>
       </c>
       <c r="P3">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.17499999999999999</v>
       </c>
       <c r="Q3" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>5.8000000000000003E-2</v>
       </c>
       <c r="R3">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>3</v>
       </c>
       <c r="S3" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.4810764252159561</v>
       </c>
       <c r="U3">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.11280000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>2</v>
       </c>
@@ -5803,27 +5894,27 @@
         <v>60</v>
       </c>
       <c r="P4">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.17699999999999999</v>
       </c>
       <c r="Q4" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="R4">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="S4" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2824211248367834</v>
       </c>
       <c r="U4">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>8.950000000000001E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
@@ -5865,27 +5956,27 @@
         <v>60</v>
       </c>
       <c r="P5">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.19400000000000001</v>
       </c>
       <c r="Q5" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.2999999999999995E-2</v>
       </c>
       <c r="R5">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="S5" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5037468096694409</v>
       </c>
       <c r="U5">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.1600000000000011E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
@@ -5929,27 +6020,27 @@
         <v>60</v>
       </c>
       <c r="P6">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.21199999999999999</v>
       </c>
       <c r="Q6" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.9000000000000001E-2</v>
       </c>
       <c r="R6">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2.6669999999999998</v>
       </c>
       <c r="S6" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7358822754666079</v>
       </c>
       <c r="U6">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.9100000000000014E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
@@ -5991,27 +6082,27 @@
         <v>80</v>
       </c>
       <c r="P7">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.19700000000000001</v>
       </c>
       <c r="Q7" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>8.6999999999999994E-2</v>
       </c>
       <c r="R7">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2.25</v>
       </c>
       <c r="S7" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.1994111254096289</v>
       </c>
       <c r="U7">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.2000000000000018E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
@@ -6032,11 +6123,11 @@
         <v>800</v>
       </c>
       <c r="G8">
-        <f>100/C8*B8*E8</f>
+        <f t="shared" si="1"/>
         <v>7.9365079365079358</v>
       </c>
       <c r="H8" s="2">
-        <f>G8*100/F8</f>
+        <f t="shared" si="2"/>
         <v>0.99206349206349198</v>
       </c>
       <c r="I8" s="12"/>
@@ -6053,32 +6144,32 @@
         <v>70</v>
       </c>
       <c r="P8">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.23100000000000001</v>
       </c>
       <c r="Q8" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>9.5000000000000001E-2</v>
       </c>
       <c r="R8">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2.4289999999999998</v>
       </c>
       <c r="S8" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7644743345149241</v>
       </c>
       <c r="U8">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.0300000000000011E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B9" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C9" s="1">
         <v>60</v>
@@ -6091,15 +6182,15 @@
         <v>1</v>
       </c>
       <c r="F9" s="1">
-        <v>1100</v>
+        <v>1500</v>
       </c>
       <c r="G9">
-        <f>100/C9*B9*E9</f>
-        <v>16.666666666666668</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
       <c r="H9" s="2">
-        <f>G9*100/F9</f>
-        <v>1.5151515151515151</v>
+        <f t="shared" si="2"/>
+        <v>1.6666666666666667</v>
       </c>
       <c r="I9" s="14"/>
       <c r="L9">
@@ -6115,27 +6206,27 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.20699999999999999</v>
       </c>
       <c r="Q9" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.104</v>
       </c>
       <c r="R9">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2</v>
       </c>
       <c r="S9" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0725388601036268</v>
       </c>
       <c r="U9">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.400000000000002E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L10">
         <v>9</v>
       </c>
@@ -6149,27 +6240,27 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.22600000000000001</v>
       </c>
       <c r="Q10" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.113</v>
       </c>
       <c r="R10">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>2</v>
       </c>
       <c r="S10" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2598870056497176</v>
       </c>
       <c r="U10">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>6.3100000000000017E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -6177,36 +6268,36 @@
         <v>10</v>
       </c>
       <c r="M11">
-        <v>965</v>
+        <v>885</v>
       </c>
       <c r="N11">
-        <v>220</v>
+        <v>360</v>
       </c>
       <c r="O11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="P11">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.22800000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.40699999999999997</v>
       </c>
       <c r="Q11" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.124</v>
       </c>
       <c r="R11">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.833</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>3.2730000000000001</v>
       </c>
       <c r="S11" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.081156522472134</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.8784918884566468</v>
       </c>
       <c r="U11">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.760000000000003E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -6238,36 +6329,36 @@
         <v>11</v>
       </c>
       <c r="M12">
-        <v>865</v>
+        <v>975</v>
       </c>
       <c r="N12">
-        <v>220</v>
+        <v>460</v>
       </c>
       <c r="O12">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="P12">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.254</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.47199999999999998</v>
       </c>
       <c r="Q12" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.13900000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.13800000000000001</v>
       </c>
       <c r="R12">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.833</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>3.407</v>
       </c>
       <c r="S12" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.3217526522376981</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>4.0605637361946707</v>
       </c>
       <c r="U12">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>9.7500000000000003E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
         <v>0</v>
       </c>
@@ -6288,11 +6379,11 @@
         <v>830</v>
       </c>
       <c r="G13">
-        <f>100/C13*B13*E13</f>
+        <f>100/C13*B13</f>
         <v>15.384615384615385</v>
       </c>
       <c r="H13" s="2">
-        <f>G13*100/F13</f>
+        <f>G13*100*E13/F13</f>
         <v>1.8535681186283597</v>
       </c>
       <c r="I13" s="10"/>
@@ -6309,27 +6400,27 @@
         <v>120</v>
       </c>
       <c r="P13">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.28000000000000003</v>
       </c>
       <c r="Q13" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.153</v>
       </c>
       <c r="R13">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>1.833</v>
       </c>
       <c r="S13" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.558364387497591</v>
       </c>
       <c r="U13">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.12280000000000005</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>1</v>
       </c>
@@ -6350,11 +6441,11 @@
         <v>2150</v>
       </c>
       <c r="G14">
-        <f t="shared" ref="G14:G19" si="4">100/C14*B14*E14</f>
-        <v>38.171428571428571</v>
+        <f t="shared" ref="G14:G20" si="4">100/C14*B14</f>
+        <v>11.428571428571429</v>
       </c>
       <c r="H14" s="2">
-        <f t="shared" ref="H14:H19" si="5">G14*100/F14</f>
+        <f t="shared" ref="H14:H20" si="5">G14*100*E14/F14</f>
         <v>1.7754152823920264</v>
       </c>
       <c r="I14" s="11" t="s">
@@ -6364,36 +6455,36 @@
         <v>13</v>
       </c>
       <c r="M14">
-        <v>875</v>
+        <v>1020</v>
       </c>
       <c r="N14">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="O14">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="P14">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.28599999999999998</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.49</v>
       </c>
       <c r="Q14" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.17100000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.17199999999999999</v>
       </c>
       <c r="R14">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.667</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>2.8570000000000002</v>
       </c>
       <c r="S14" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.3328473740792175</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.7055340491100708</v>
       </c>
       <c r="U14">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.15350000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
         <v>2</v>
       </c>
@@ -6435,27 +6526,27 @@
         <v>150</v>
       </c>
       <c r="P15">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.33100000000000002</v>
       </c>
       <c r="Q15" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.19900000000000001</v>
       </c>
       <c r="R15">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>1.667</v>
       </c>
       <c r="S15" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7036310626745901</v>
       </c>
       <c r="U15">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.18960000000000002</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>3</v>
       </c>
@@ -6492,33 +6583,33 @@
         <v>785</v>
       </c>
       <c r="N16">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="O16">
         <v>185</v>
       </c>
       <c r="P16">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.36299999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.45900000000000002</v>
       </c>
       <c r="Q16" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.23599999999999999</v>
       </c>
       <c r="R16">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.5409999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.946</v>
       </c>
       <c r="S16" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.6692505388119132</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.3716848911308377</v>
       </c>
       <c r="U16">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.2311</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>4</v>
       </c>
@@ -6540,11 +6631,11 @@
       </c>
       <c r="G17">
         <f t="shared" si="4"/>
-        <v>29.217391304347824</v>
+        <v>17.391304347826086</v>
       </c>
       <c r="H17" s="2">
         <f t="shared" si="5"/>
-        <v>1.3280632411067192</v>
+        <v>1.328063241106719</v>
       </c>
       <c r="I17" s="13" t="s">
         <v>40</v>
@@ -6562,27 +6653,27 @@
         <v>220</v>
       </c>
       <c r="P17">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.38800000000000001</v>
       </c>
       <c r="Q17" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.26700000000000002</v>
       </c>
       <c r="R17">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>1.4550000000000001</v>
       </c>
       <c r="S17" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.6150782544028783</v>
       </c>
       <c r="U17">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.27800000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>5</v>
       </c>
@@ -6618,33 +6709,33 @@
         <v>925</v>
       </c>
       <c r="N18">
-        <v>380</v>
+        <v>680</v>
       </c>
       <c r="O18">
         <v>280</v>
       </c>
       <c r="P18">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.41099999999999998</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.73499999999999999</v>
       </c>
       <c r="Q18" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.30299999999999999</v>
       </c>
       <c r="R18">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.357</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>2.4289999999999998</v>
       </c>
       <c r="S18" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.4550641705247003</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>4.3932727262020954</v>
       </c>
       <c r="U18">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.33030000000000004</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>35</v>
       </c>
@@ -6680,38 +6771,38 @@
         <v>830</v>
       </c>
       <c r="N19">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="O19">
         <v>300</v>
       </c>
       <c r="P19">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.48199999999999998</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.66300000000000003</v>
       </c>
       <c r="Q19" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.36099999999999999</v>
       </c>
       <c r="R19">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.333</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.833</v>
       </c>
       <c r="S19" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.7824109358536178</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.8258150367987249</v>
       </c>
       <c r="U19">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.38800000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="1">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C20" s="1">
         <v>60</v>
@@ -6724,15 +6815,16 @@
         <v>1.68</v>
       </c>
       <c r="F20" s="1">
-        <v>3250</v>
+        <f>1500+900+450+1300</f>
+        <v>4150</v>
       </c>
       <c r="G20">
-        <f>100/C20*B20*E20</f>
-        <v>56</v>
+        <f t="shared" si="4"/>
+        <v>46.666666666666671</v>
       </c>
       <c r="H20" s="2">
-        <f>G20*100/F20</f>
-        <v>1.7230769230769232</v>
+        <f t="shared" si="5"/>
+        <v>1.889156626506024</v>
       </c>
       <c r="I20" s="14"/>
       <c r="L20">
@@ -6742,33 +6834,33 @@
         <v>975</v>
       </c>
       <c r="N20">
-        <v>520</v>
+        <v>670</v>
       </c>
       <c r="O20">
         <v>420</v>
       </c>
       <c r="P20">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.53300000000000003</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.68700000000000006</v>
       </c>
       <c r="Q20" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.43099999999999999</v>
       </c>
       <c r="R20">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.238</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.595</v>
       </c>
       <c r="S20" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.6024001945294217</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.3530925583359856</v>
       </c>
       <c r="U20">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.45109999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L21">
         <v>20</v>
       </c>
@@ -6776,33 +6868,33 @@
         <v>795</v>
       </c>
       <c r="N21">
-        <v>440</v>
+        <v>590</v>
       </c>
       <c r="O21">
         <v>400</v>
       </c>
       <c r="P21">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.55300000000000005</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.74199999999999999</v>
       </c>
       <c r="Q21" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.503</v>
       </c>
       <c r="R21">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>1.1000000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.4750000000000001</v>
       </c>
       <c r="S21" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.767295597484277</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.7106918238993711</v>
       </c>
       <c r="U21">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.51960000000000006</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>21</v>
       </c>
@@ -6816,27 +6908,27 @@
         <v>540</v>
       </c>
       <c r="P22">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.60699999999999998</v>
       </c>
       <c r="Q22" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.56499999999999995</v>
       </c>
       <c r="R22">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>1.0740000000000001</v>
       </c>
       <c r="S22" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.6135315192557318</v>
       </c>
       <c r="U22">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.59350000000000014</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>22</v>
       </c>
@@ -6844,33 +6936,33 @@
         <v>955</v>
       </c>
       <c r="N23">
-        <v>540</v>
+        <v>870</v>
       </c>
       <c r="O23">
         <v>590</v>
       </c>
       <c r="P23">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.56499999999999995</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.91100000000000003</v>
       </c>
       <c r="Q23" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.61799999999999999</v>
       </c>
       <c r="R23">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.91500000000000004</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.4750000000000001</v>
       </c>
       <c r="S23" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.3279003328796541</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.7505060918616642</v>
       </c>
       <c r="U23">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.67279999999999995</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
         <v>26</v>
       </c>
@@ -6899,39 +6991,39 @@
         <v>650</v>
       </c>
       <c r="P24">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.66300000000000003</v>
       </c>
       <c r="Q24" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.71799999999999997</v>
       </c>
       <c r="R24">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.92300000000000004</v>
       </c>
       <c r="S24" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.6004349410587939</v>
       </c>
       <c r="U24">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.75750000000000006</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="C25">
         <v>50</v>
       </c>
       <c r="D25">
         <f>B25/C25</f>
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25" t="s">
         <v>34</v>
@@ -6946,45 +7038,45 @@
         <v>765</v>
       </c>
       <c r="N25">
-        <v>531</v>
+        <v>861</v>
       </c>
       <c r="O25">
         <v>620</v>
       </c>
       <c r="P25">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.69399999999999995</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.125</v>
       </c>
       <c r="Q25" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.81</v>
       </c>
       <c r="R25">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.85599999999999998</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.389</v>
       </c>
       <c r="S25" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.7876435532498487</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>4.5200773999022976</v>
       </c>
       <c r="U25">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.84760000000000013</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26">
-        <v>1700</v>
+        <v>1550</v>
       </c>
       <c r="C26">
         <v>80</v>
       </c>
       <c r="D26">
         <f t="shared" ref="D26:D29" si="6">B26/C26</f>
-        <v>21.25</v>
+        <v>19.375</v>
       </c>
       <c r="L26">
         <v>25</v>
@@ -6993,45 +7085,45 @@
         <v>935</v>
       </c>
       <c r="N26">
-        <v>730</v>
+        <v>895</v>
       </c>
       <c r="O26">
         <v>840</v>
       </c>
       <c r="P26">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.78100000000000003</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>0.95699999999999996</v>
       </c>
       <c r="Q26" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.89800000000000002</v>
       </c>
       <c r="R26">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.86899999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>1.0649999999999999</v>
       </c>
       <c r="S26" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.6938388145450194</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.3027201904353323</v>
       </c>
       <c r="U26">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>0.94310000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27">
-        <v>2200</v>
+        <v>2000</v>
       </c>
       <c r="C27">
         <v>110</v>
       </c>
       <c r="D27">
         <f t="shared" si="6"/>
-        <v>20</v>
+        <v>18.181818181818183</v>
       </c>
       <c r="L27">
         <v>26</v>
@@ -7046,39 +7138,39 @@
         <v>800</v>
       </c>
       <c r="P27">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.86299999999999999</v>
       </c>
       <c r="Q27" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1</v>
       </c>
       <c r="R27">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.86299999999999999</v>
       </c>
       <c r="S27" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.049397993866986</v>
       </c>
       <c r="U27">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.0440000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
       <c r="B28">
-        <v>2700</v>
+        <v>2450</v>
       </c>
       <c r="C28">
         <v>140</v>
       </c>
       <c r="D28">
         <f t="shared" si="6"/>
-        <v>19.285714285714285</v>
+        <v>17.5</v>
       </c>
       <c r="L28">
         <v>27</v>
@@ -7093,39 +7185,39 @@
         <v>1025</v>
       </c>
       <c r="P28">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.91200000000000003</v>
       </c>
       <c r="Q28" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.133</v>
       </c>
       <c r="R28">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.80500000000000005</v>
       </c>
       <c r="S28" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.8473669294607737</v>
       </c>
       <c r="U28">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.1503000000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
       <c r="B29">
-        <v>4200</v>
+        <v>3750</v>
       </c>
       <c r="C29">
         <v>240</v>
       </c>
       <c r="D29">
         <f t="shared" si="6"/>
-        <v>17.5</v>
+        <v>15.625</v>
       </c>
       <c r="G29" t="s">
         <v>23</v>
@@ -7143,27 +7235,27 @@
         <v>1100</v>
       </c>
       <c r="P29">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>0.98299999999999998</v>
       </c>
       <c r="Q29" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.2430000000000001</v>
       </c>
       <c r="R29">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.79100000000000004</v>
       </c>
       <c r="S29" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.9640098280525917</v>
       </c>
       <c r="U29">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.262</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>29</v>
       </c>
@@ -7177,27 +7269,27 @@
         <v>1000</v>
       </c>
       <c r="P30">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.0069999999999999</v>
       </c>
       <c r="Q30" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.361</v>
       </c>
       <c r="R30">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.74</v>
       </c>
       <c r="S30" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.183789753094695</v>
       </c>
       <c r="U30">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.3791000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L31">
         <v>30</v>
       </c>
@@ -7211,95 +7303,95 @@
         <v>1500</v>
       </c>
       <c r="P31">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.359</v>
       </c>
       <c r="Q31" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5629999999999999</v>
       </c>
       <c r="R31">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.87</v>
       </c>
       <c r="S31" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.5098911575004714</v>
       </c>
       <c r="U31">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.5016</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>31</v>
       </c>
       <c r="M32">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="N32">
-        <v>730</v>
+        <v>1285</v>
       </c>
       <c r="O32">
         <v>1600</v>
       </c>
       <c r="P32">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.74099999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.3089999999999999</v>
       </c>
       <c r="Q32" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>1.6240000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.629</v>
       </c>
       <c r="R32">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.45600000000000002</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.80300000000000005</v>
       </c>
       <c r="S32" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>1.8527918781725889</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.2713849287169041</v>
       </c>
       <c r="U32">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.6294999999999999</v>
       </c>
     </row>
-    <row r="33" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>32</v>
       </c>
       <c r="M33">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N33">
-        <v>782</v>
+        <v>1152</v>
       </c>
       <c r="O33">
         <v>1490</v>
       </c>
       <c r="P33">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.93200000000000005</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.371</v>
       </c>
       <c r="Q33" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>1.776</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.774</v>
       </c>
       <c r="R33">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.52500000000000002</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.77300000000000002</v>
       </c>
       <c r="S33" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.4146359263287054</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.5528760696057584</v>
       </c>
       <c r="U33">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.7628000000000001</v>
       </c>
     </row>
-    <row r="34" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>33</v>
       </c>
@@ -7307,101 +7399,155 @@
         <v>945</v>
       </c>
       <c r="N34">
-        <v>840</v>
+        <v>1210</v>
       </c>
       <c r="O34">
         <v>1800</v>
       </c>
       <c r="P34">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.88900000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.28</v>
       </c>
       <c r="Q34" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.905</v>
       </c>
       <c r="R34">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.46700000000000003</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.67200000000000004</v>
       </c>
       <c r="S34" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.0951312035156961</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.0179866145880863</v>
       </c>
       <c r="U34">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>1.9015000000000002</v>
       </c>
     </row>
-    <row r="35" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>34</v>
       </c>
       <c r="M35">
-        <v>775</v>
+        <v>801</v>
       </c>
       <c r="N35">
-        <v>616</v>
+        <v>1001</v>
       </c>
       <c r="O35">
-        <v>1600</v>
+        <v>1650</v>
       </c>
       <c r="P35">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.79500000000000004</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.25</v>
       </c>
       <c r="Q35" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>2.0649999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.06</v>
       </c>
       <c r="R35">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.38500000000000001</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.60699999999999998</v>
       </c>
       <c r="S35" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>1.9870967741935481</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.0765189131164057</v>
       </c>
       <c r="U35">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.0456000000000003</v>
       </c>
     </row>
-    <row r="36" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>11</v>
+      </c>
+      <c r="H36" t="s">
+        <v>12</v>
+      </c>
       <c r="L36">
         <v>35</v>
       </c>
       <c r="M36">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="N36">
-        <v>840</v>
+        <v>1580</v>
       </c>
       <c r="O36">
         <v>1800</v>
       </c>
       <c r="P36">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>1.018</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.913</v>
       </c>
       <c r="Q36" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>2.1819999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.1789999999999998</v>
       </c>
       <c r="R36">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.46700000000000003</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.878</v>
       </c>
       <c r="S36" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.3998775603907063</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>4.5085904530861383</v>
       </c>
       <c r="U36">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.1951000000000001</v>
       </c>
     </row>
-    <row r="37" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B37" s="1">
+        <f>B13+1</f>
+        <v>3</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" ref="C37" si="7">C13</f>
+        <v>13</v>
+      </c>
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37">
+        <f>ROUND(D37^0.75, 2)</f>
+        <v>1.68</v>
+      </c>
+      <c r="F37" s="1">
+        <f>F13+1000</f>
+        <v>1830</v>
+      </c>
+      <c r="G37">
+        <f>100/C37*B37</f>
+        <v>23.076923076923077</v>
+      </c>
+      <c r="H37" s="2">
+        <f>G37*E37*100/F37</f>
+        <v>2.1185372005044134</v>
+      </c>
       <c r="L37">
         <v>36</v>
       </c>
@@ -7415,95 +7561,188 @@
         <v>2000</v>
       </c>
       <c r="P37">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.272</v>
       </c>
       <c r="Q37" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.3119999999999998</v>
       </c>
       <c r="R37">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.55000000000000004</v>
       </c>
       <c r="S37" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.8435546534679408</v>
       </c>
       <c r="U37">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.3500000000000005</v>
       </c>
     </row>
-    <row r="38" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="1">
+        <f>B13+2</f>
+        <v>4</v>
+      </c>
+      <c r="C38" s="1">
+        <f>C13-3</f>
+        <v>10</v>
+      </c>
+      <c r="D38" s="1">
+        <f t="shared" ref="D38" si="8">D13</f>
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <f>ROUND(D38^0.75, 2)</f>
+        <v>1</v>
+      </c>
+      <c r="F38" s="1">
+        <f>F13+1100</f>
+        <v>1930</v>
+      </c>
+      <c r="G38">
+        <f>100/C38*B38</f>
+        <v>40</v>
+      </c>
+      <c r="H38" s="2">
+        <f>G38*E38*100/F38</f>
+        <v>2.0725388601036268</v>
+      </c>
       <c r="L38">
         <v>37</v>
       </c>
       <c r="M38">
-        <v>995</v>
+        <v>998</v>
       </c>
       <c r="N38">
-        <v>1210</v>
+        <v>1765</v>
       </c>
       <c r="O38">
         <v>2500</v>
       </c>
       <c r="P38">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>1.216</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.7689999999999999</v>
       </c>
       <c r="Q38" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>2.5129999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.5049999999999999</v>
       </c>
       <c r="R38">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.48399999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.70599999999999996</v>
       </c>
       <c r="S38" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.4321608040201004</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.5370741482965937</v>
       </c>
       <c r="U38">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.5103000000000009</v>
       </c>
     </row>
-    <row r="39" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="1">
+        <f>B14+1</f>
+        <v>5</v>
+      </c>
+      <c r="C39" s="1">
+        <f>C14-10</f>
+        <v>25</v>
+      </c>
+      <c r="D39" s="1">
+        <f t="shared" ref="D39" si="9">D14</f>
+        <v>5</v>
+      </c>
+      <c r="E39">
+        <f>ROUND(D39^0.75, 2)</f>
+        <v>3.34</v>
+      </c>
+      <c r="F39" s="1">
+        <f>F14+1000</f>
+        <v>3150</v>
+      </c>
+      <c r="G39">
+        <f>100/C39*B39</f>
+        <v>20</v>
+      </c>
+      <c r="H39" s="2">
+        <f>G39*E39*100/F39</f>
+        <v>2.1206349206349207</v>
+      </c>
       <c r="L39">
         <v>38</v>
       </c>
       <c r="M39">
-        <v>920</v>
+        <v>923</v>
       </c>
       <c r="N39">
-        <v>1185</v>
+        <v>1740</v>
       </c>
       <c r="O39">
         <v>2450</v>
       </c>
       <c r="P39">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>1.288</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.885</v>
       </c>
       <c r="Q39" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
-        <v>2.6629999999999998</v>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.6539999999999999</v>
       </c>
       <c r="R39">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.48399999999999999</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.71</v>
       </c>
       <c r="S39" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>2.6022407941181953</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.80859247566814</v>
       </c>
       <c r="U39">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.6760000000000002</v>
       </c>
     </row>
-    <row r="40" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="1">
+        <f>B14+4</f>
+        <v>8</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" ref="C40" si="10">C14</f>
+        <v>35</v>
+      </c>
+      <c r="D40" s="1">
+        <f>D14+2</f>
+        <v>7</v>
+      </c>
+      <c r="E40">
+        <f>ROUND(D40^0.75, 2)</f>
+        <v>4.3</v>
+      </c>
+      <c r="F40" s="1">
+        <f>F14+1700</f>
+        <v>3850</v>
+      </c>
+      <c r="G40">
+        <f>100/C40*B40</f>
+        <v>22.857142857142858</v>
+      </c>
+      <c r="H40" s="2">
+        <f>G40*E40*100/F40</f>
+        <v>2.5528756957328382</v>
+      </c>
       <c r="L40">
         <v>39</v>
       </c>
@@ -7511,33 +7750,63 @@
         <v>845</v>
       </c>
       <c r="N40">
-        <v>820</v>
+        <v>1930</v>
       </c>
       <c r="O40">
         <v>2400</v>
       </c>
       <c r="P40">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
-        <v>0.97</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.2839999999999998</v>
       </c>
       <c r="Q40" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.84</v>
       </c>
       <c r="R40">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
-        <v>0.34200000000000003</v>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.80400000000000005</v>
       </c>
       <c r="S40" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
-        <v>1.9808496933749566</v>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>4.6622437905044718</v>
       </c>
       <c r="U40">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>2.8471000000000002</v>
       </c>
     </row>
-    <row r="41" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="1">
+        <f>B15+1</f>
+        <v>3</v>
+      </c>
+      <c r="C41" s="1">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1">
+        <f t="shared" ref="D41" si="11">D15</f>
+        <v>1</v>
+      </c>
+      <c r="E41">
+        <f t="shared" ref="E41:E44" si="12">ROUND(D41^0.75, 2)</f>
+        <v>1</v>
+      </c>
+      <c r="F41" s="1">
+        <f>F15+1100</f>
+        <v>2370</v>
+      </c>
+      <c r="G41">
+        <f t="shared" ref="G41:G42" si="13">100/C41*B41</f>
+        <v>50</v>
+      </c>
+      <c r="H41" s="2">
+        <f t="shared" ref="H41:H42" si="14">G41*E41*100/F41</f>
+        <v>2.109704641350211</v>
+      </c>
       <c r="L41">
         <v>40</v>
       </c>
@@ -7551,27 +7820,58 @@
         <v>2900</v>
       </c>
       <c r="P41">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5940000000000001</v>
       </c>
       <c r="Q41" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.0209999999999999</v>
       </c>
       <c r="R41">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.52800000000000002</v>
       </c>
       <c r="S41" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.9595194521967643</v>
       </c>
       <c r="U41">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.0236000000000005</v>
       </c>
     </row>
-    <row r="42" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="1">
+        <f>B15+2</f>
+        <v>4</v>
+      </c>
+      <c r="C42" s="1">
+        <f>C15+1</f>
+        <v>10</v>
+      </c>
+      <c r="D42" s="1">
+        <f t="shared" ref="D42" si="15">D15</f>
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="1">
+        <f>F15+1000</f>
+        <v>2270</v>
+      </c>
+      <c r="G42">
+        <f t="shared" si="13"/>
+        <v>40</v>
+      </c>
+      <c r="H42" s="2">
+        <f t="shared" si="14"/>
+        <v>1.7621145374449338</v>
+      </c>
       <c r="L42">
         <v>41</v>
       </c>
@@ -7585,27 +7885,58 @@
         <v>3000</v>
       </c>
       <c r="P42">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.401</v>
       </c>
       <c r="Q42" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.2090000000000001</v>
       </c>
       <c r="R42">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.437</v>
       </c>
       <c r="S42" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5579912667799203</v>
       </c>
       <c r="U42">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.2055000000000007</v>
       </c>
     </row>
-    <row r="43" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B43" s="1">
+        <f>B16+5</f>
+        <v>10</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" ref="C43:D43" si="16">C16</f>
+        <v>30</v>
+      </c>
+      <c r="D43" s="1">
+        <f t="shared" si="16"/>
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="F43" s="1">
+        <f>F16+800</f>
+        <v>2410</v>
+      </c>
+      <c r="G43">
+        <f t="shared" ref="G43:G44" si="17">100/C43*B43</f>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="H43" s="2">
+        <f t="shared" ref="H43:H44" si="18">G43*E43*100/F43</f>
+        <v>1.3831258644536653</v>
+      </c>
       <c r="L43">
         <v>42</v>
       </c>
@@ -7619,27 +7950,57 @@
         <v>2800</v>
       </c>
       <c r="P43">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.2609999999999999</v>
       </c>
       <c r="Q43" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.3940000000000001</v>
       </c>
       <c r="R43">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.371</v>
       </c>
       <c r="S43" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.382321526846038</v>
       </c>
       <c r="U43">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.3928000000000007</v>
       </c>
     </row>
-    <row r="44" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="1">
+        <f>B16</f>
+        <v>5</v>
+      </c>
+      <c r="C44" s="1">
+        <v>16</v>
+      </c>
+      <c r="D44" s="1">
+        <f t="shared" ref="D44" si="19">D16</f>
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="F44" s="1">
+        <f>F16+700</f>
+        <v>2310</v>
+      </c>
+      <c r="G44">
+        <f t="shared" si="17"/>
+        <v>31.25</v>
+      </c>
+      <c r="H44" s="2">
+        <f t="shared" si="18"/>
+        <v>1.3528138528138529</v>
+      </c>
       <c r="L44">
         <v>43</v>
       </c>
@@ -7653,27 +8014,27 @@
         <v>2600</v>
       </c>
       <c r="P44">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5449999999999999</v>
       </c>
       <c r="Q44" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.5859999999999999</v>
       </c>
       <c r="R44">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.43099999999999999</v>
       </c>
       <c r="S44" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.0296561566174636</v>
       </c>
       <c r="U44">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.5855000000000006</v>
       </c>
     </row>
-    <row r="45" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L45">
         <v>44</v>
       </c>
@@ -7687,27 +8048,27 @@
         <v>3000</v>
       </c>
       <c r="P45">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.101</v>
       </c>
       <c r="Q45" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.774</v>
       </c>
       <c r="R45">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.29199999999999998</v>
       </c>
       <c r="S45" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0094643095053262</v>
       </c>
       <c r="U45">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.7835999999999999</v>
       </c>
     </row>
-    <row r="46" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L46">
         <v>45</v>
       </c>
@@ -7721,27 +8082,27 @@
         <v>3500</v>
       </c>
       <c r="P46">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.04</v>
       </c>
       <c r="Q46" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.9769999999999999</v>
       </c>
       <c r="R46">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.51300000000000001</v>
       </c>
       <c r="S46" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.4478451982674705</v>
       </c>
       <c r="U46">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>3.9871000000000008</v>
       </c>
     </row>
-    <row r="47" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L47">
         <v>46</v>
       </c>
@@ -7755,27 +8116,27 @@
         <v>3000</v>
       </c>
       <c r="P47">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.58</v>
       </c>
       <c r="Q47" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>4.1959999999999997</v>
       </c>
       <c r="R47">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.377</v>
       </c>
       <c r="S47" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.8854381817288473</v>
       </c>
       <c r="U47">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>4.1960000000000006</v>
       </c>
     </row>
-    <row r="48" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
       <c r="L48">
         <v>47</v>
       </c>
@@ -7789,27 +8150,27 @@
         <v>4000</v>
       </c>
       <c r="P48">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.2150000000000001</v>
       </c>
       <c r="Q48" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>4.42</v>
       </c>
       <c r="R48">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.27500000000000002</v>
       </c>
       <c r="S48" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.9218262023122747</v>
       </c>
       <c r="U48">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>4.4103000000000003</v>
       </c>
     </row>
-    <row r="49" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L49">
         <v>48</v>
       </c>
@@ -7823,27 +8184,27 @@
         <v>4000</v>
       </c>
       <c r="P49">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5029999999999999</v>
       </c>
       <c r="Q49" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>4.6239999999999997</v>
       </c>
       <c r="R49">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.32500000000000001</v>
       </c>
       <c r="S49" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.3762780105311521</v>
       </c>
       <c r="U49">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>4.6300000000000008</v>
       </c>
     </row>
-    <row r="50" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L50">
         <v>49</v>
       </c>
@@ -7857,27 +8218,27 @@
         <v>4550</v>
       </c>
       <c r="P50">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5609999999999999</v>
       </c>
       <c r="Q50" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>4.8559999999999999</v>
       </c>
       <c r="R50">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.32200000000000001</v>
       </c>
       <c r="S50" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.3147230528819445</v>
       </c>
       <c r="U50">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>4.8551000000000011</v>
       </c>
     </row>
-    <row r="51" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L51">
         <v>50</v>
       </c>
@@ -7891,27 +8252,27 @@
         <v>4800</v>
       </c>
       <c r="P51">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.915</v>
       </c>
       <c r="Q51" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>5.0789999999999997</v>
       </c>
       <c r="R51">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.377</v>
       </c>
       <c r="S51" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7645608127863031</v>
       </c>
       <c r="U51">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.0856000000000003</v>
       </c>
     </row>
-    <row r="52" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L52">
         <v>51</v>
       </c>
@@ -7925,27 +8286,27 @@
         <v>4500</v>
       </c>
       <c r="P52">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.538</v>
       </c>
       <c r="Q52" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>5.3250000000000002</v>
       </c>
       <c r="R52">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.28899999999999998</v>
       </c>
       <c r="S52" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2934030538459385</v>
       </c>
       <c r="U52">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.3215000000000003</v>
       </c>
     </row>
-    <row r="53" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L53">
         <v>52</v>
       </c>
@@ -7959,27 +8320,27 @@
         <v>5000</v>
       </c>
       <c r="P53">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.173</v>
       </c>
       <c r="Q53" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>5.5869999999999997</v>
       </c>
       <c r="R53">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.21</v>
       </c>
       <c r="S53" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.6591332295997203</v>
       </c>
       <c r="U53">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.5628000000000011</v>
       </c>
     </row>
-    <row r="54" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L54">
         <v>53</v>
       </c>
@@ -7993,27 +8354,27 @@
         <v>4500</v>
       </c>
       <c r="P54">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.871</v>
       </c>
       <c r="Q54" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>5.806</v>
       </c>
       <c r="R54">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.32200000000000001</v>
       </c>
       <c r="S54" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7890740364513507</v>
       </c>
       <c r="U54">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>5.8095000000000008</v>
       </c>
     </row>
-    <row r="55" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L55">
         <v>54</v>
       </c>
@@ -8027,27 +8388,27 @@
         <v>5800</v>
       </c>
       <c r="P55">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.0939999999999999</v>
       </c>
       <c r="Q55" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>6.0730000000000004</v>
       </c>
       <c r="R55">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.34499999999999997</v>
       </c>
       <c r="S55" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7498729394706292</v>
       </c>
       <c r="U55">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>6.0616000000000012</v>
       </c>
     </row>
-    <row r="56" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L56">
         <v>55</v>
       </c>
@@ -8061,27 +8422,27 @@
         <v>5400</v>
       </c>
       <c r="P56">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.76</v>
       </c>
       <c r="Q56" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>6.3159999999999998</v>
       </c>
       <c r="R56">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.437</v>
       </c>
       <c r="S56" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.7562025945213122</v>
       </c>
       <c r="U56">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>6.3191000000000006</v>
       </c>
     </row>
-    <row r="57" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L57">
         <v>56</v>
       </c>
@@ -8095,27 +8456,27 @@
         <v>6000</v>
       </c>
       <c r="P57">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.913</v>
       </c>
       <c r="Q57" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>6.5570000000000004</v>
       </c>
       <c r="R57">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.29199999999999998</v>
       </c>
       <c r="S57" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.4691150658881527</v>
       </c>
       <c r="U57">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>6.5819999999999999</v>
       </c>
     </row>
-    <row r="58" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L58">
         <v>57</v>
       </c>
@@ -8129,27 +8490,27 @@
         <v>6100</v>
       </c>
       <c r="P58">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.706</v>
       </c>
       <c r="Q58" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>6.8929999999999998</v>
       </c>
       <c r="R58">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.248</v>
       </c>
       <c r="S58" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.1845840530923493</v>
       </c>
       <c r="U58">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>6.8503000000000016</v>
       </c>
     </row>
-    <row r="59" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L59">
         <v>58</v>
       </c>
@@ -8163,27 +8524,27 @@
         <v>7000</v>
       </c>
       <c r="P59">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.234</v>
       </c>
       <c r="Q59" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.1070000000000002</v>
       </c>
       <c r="R59">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.314</v>
       </c>
       <c r="S59" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.6695461325235188</v>
       </c>
       <c r="U59">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.1240000000000014</v>
       </c>
     </row>
-    <row r="60" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L60">
         <v>59</v>
       </c>
@@ -8197,27 +8558,27 @@
         <v>5000</v>
       </c>
       <c r="P60">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.444</v>
       </c>
       <c r="Q60" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.407</v>
       </c>
       <c r="R60">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.19500000000000001</v>
       </c>
       <c r="S60" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0427529234278037</v>
       </c>
       <c r="U60">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.4031000000000002</v>
       </c>
     </row>
-    <row r="61" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L61">
         <v>60</v>
       </c>
@@ -8231,27 +8592,27 @@
         <v>6000</v>
       </c>
       <c r="P61">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.4650000000000001</v>
       </c>
       <c r="Q61" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.6429999999999998</v>
       </c>
       <c r="R61">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.192</v>
       </c>
       <c r="S61" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.8912657529250654</v>
       </c>
       <c r="U61">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.6876000000000007</v>
       </c>
     </row>
-    <row r="62" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L62">
         <v>61</v>
       </c>
@@ -8265,27 +8626,27 @@
         <v>6100</v>
       </c>
       <c r="P62">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.974</v>
       </c>
       <c r="Q62" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>7.9740000000000002</v>
       </c>
       <c r="R62">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.248</v>
       </c>
       <c r="S62" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5272639045578162</v>
       </c>
       <c r="U62">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>7.9775000000000018</v>
       </c>
     </row>
-    <row r="63" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L63">
         <v>62</v>
       </c>
@@ -8299,27 +8660,27 @@
         <v>6000</v>
       </c>
       <c r="P63">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.5860000000000001</v>
       </c>
       <c r="Q63" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>8.2759999999999998</v>
       </c>
       <c r="R63">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.192</v>
       </c>
       <c r="S63" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0477842979947263</v>
       </c>
       <c r="U63">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>8.2728000000000002</v>
       </c>
     </row>
-    <row r="64" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L64">
         <v>63</v>
       </c>
@@ -8333,27 +8694,27 @@
         <v>7500</v>
       </c>
       <c r="P64">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.4019999999999999</v>
       </c>
       <c r="Q64" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>8.5809999999999995</v>
       </c>
       <c r="R64">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16300000000000001</v>
       </c>
       <c r="S64" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.6184303884606215</v>
       </c>
       <c r="U64">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>8.5734999999999992</v>
       </c>
     </row>
-    <row r="65" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L65">
         <v>64</v>
       </c>
@@ -8367,27 +8728,27 @@
         <v>7300</v>
       </c>
       <c r="P65">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.903</v>
       </c>
       <c r="Q65" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>8.8480000000000008</v>
       </c>
       <c r="R65">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.215</v>
       </c>
       <c r="S65" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2273284981566666</v>
       </c>
       <c r="U65">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>8.8795999999999999</v>
       </c>
     </row>
-    <row r="66" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L66">
         <v>65</v>
       </c>
@@ -8401,27 +8762,27 @@
         <v>5200</v>
       </c>
       <c r="P66">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.319</v>
       </c>
       <c r="Q66" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>9.2040000000000006</v>
       </c>
       <c r="R66">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.252</v>
       </c>
       <c r="S66" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.2152975975887177</v>
       </c>
       <c r="U66">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>9.1911000000000005</v>
       </c>
     </row>
-    <row r="67" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L67">
         <v>66</v>
       </c>
@@ -8435,27 +8796,27 @@
         <v>5000</v>
       </c>
       <c r="P67">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.0950000000000002</v>
       </c>
       <c r="Q67" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>9.5239999999999991</v>
       </c>
       <c r="R67">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.22</v>
       </c>
       <c r="S67" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.9631141306864848</v>
       </c>
       <c r="U67">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>9.5079999999999991</v>
       </c>
     </row>
-    <row r="68" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L68">
         <v>67</v>
       </c>
@@ -8469,27 +8830,27 @@
         <v>6900</v>
       </c>
       <c r="P68">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.617</v>
       </c>
       <c r="Q68" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>9.8290000000000006</v>
       </c>
       <c r="R68">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16400000000000001</v>
       </c>
       <c r="S68" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.9464094480391461</v>
       </c>
       <c r="U68">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>9.8302999999999994</v>
       </c>
     </row>
-    <row r="69" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L69">
         <v>68</v>
       </c>
@@ -8503,27 +8864,27 @@
         <v>7000</v>
       </c>
       <c r="P69">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.8839999999999999</v>
       </c>
       <c r="Q69" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>10.145</v>
       </c>
       <c r="R69">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.186</v>
       </c>
       <c r="S69" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2518799886010314</v>
       </c>
       <c r="U69">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>10.157999999999999</v>
       </c>
     </row>
-    <row r="70" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="70" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L70">
         <v>69</v>
       </c>
@@ -8537,27 +8898,27 @@
         <v>7000</v>
       </c>
       <c r="P70">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.94</v>
       </c>
       <c r="Q70" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>10.448</v>
       </c>
       <c r="R70">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.186</v>
       </c>
       <c r="S70" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.3191002867682267</v>
       </c>
       <c r="U70">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>10.491099999999999</v>
       </c>
     </row>
-    <row r="71" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="71" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L71">
         <v>70</v>
       </c>
@@ -8571,27 +8932,27 @@
         <v>5000</v>
       </c>
       <c r="P71">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.9350000000000001</v>
       </c>
       <c r="Q71" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>10.753</v>
       </c>
       <c r="R71">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.18</v>
       </c>
       <c r="S71" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.7371875400769583</v>
       </c>
       <c r="U71">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>10.829599999999999</v>
       </c>
     </row>
-    <row r="72" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="72" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L72">
         <v>71</v>
       </c>
@@ -8605,27 +8966,27 @@
         <v>9650</v>
       </c>
       <c r="P72">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.4649999999999999</v>
       </c>
       <c r="Q72" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>11.169</v>
       </c>
       <c r="R72">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.221</v>
       </c>
       <c r="S72" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5095867012298205</v>
       </c>
       <c r="U72">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>11.173500000000001</v>
       </c>
     </row>
-    <row r="73" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="73" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L73">
         <v>72</v>
       </c>
@@ -8639,27 +9000,27 @@
         <v>8750</v>
       </c>
       <c r="P73">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.875</v>
       </c>
       <c r="Q73" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>11.513</v>
       </c>
       <c r="R73">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16300000000000001</v>
       </c>
       <c r="S73" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0044593143431828</v>
       </c>
       <c r="U73">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>11.5228</v>
       </c>
     </row>
-    <row r="74" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="74" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L74">
         <v>73</v>
       </c>
@@ -8673,27 +9034,27 @@
         <v>6500</v>
       </c>
       <c r="P74">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.1579999999999999</v>
       </c>
       <c r="Q74" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>11.84</v>
       </c>
       <c r="R74">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.182</v>
       </c>
       <c r="S74" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.6772524679091445</v>
       </c>
       <c r="U74">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>11.877500000000001</v>
       </c>
     </row>
-    <row r="75" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="75" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L75">
         <v>74</v>
       </c>
@@ -8707,27 +9068,27 @@
         <v>8500</v>
       </c>
       <c r="P75">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.9059999999999999</v>
       </c>
       <c r="Q75" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>12.23</v>
       </c>
       <c r="R75">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.156</v>
       </c>
       <c r="S75" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.0678622777677655</v>
       </c>
       <c r="U75">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>12.2376</v>
       </c>
     </row>
-    <row r="76" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="76" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L76">
         <v>75</v>
       </c>
@@ -8741,27 +9102,27 @@
         <v>9000</v>
       </c>
       <c r="P76">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>1.774</v>
       </c>
       <c r="Q76" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>12.57</v>
       </c>
       <c r="R76">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.14099999999999999</v>
       </c>
       <c r="S76" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>1.8696893055930364</v>
       </c>
       <c r="U76">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>12.6031</v>
       </c>
     </row>
-    <row r="77" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="77" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L77">
         <v>76</v>
       </c>
@@ -8775,27 +9136,27 @@
         <v>8400</v>
       </c>
       <c r="P77">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.1019999999999999</v>
       </c>
       <c r="Q77" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>12.983000000000001</v>
       </c>
       <c r="R77">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16200000000000001</v>
       </c>
       <c r="S77" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.2934801446750361</v>
       </c>
       <c r="U77">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>12.974</v>
       </c>
     </row>
-    <row r="78" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="78" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L78">
         <v>77</v>
       </c>
@@ -8809,27 +9170,27 @@
         <v>12100</v>
       </c>
       <c r="P78">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.331</v>
       </c>
       <c r="Q78" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>13.37</v>
       </c>
       <c r="R78">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.17399999999999999</v>
       </c>
       <c r="S78" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.1195379206428928</v>
       </c>
       <c r="U78">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>13.350300000000001</v>
       </c>
     </row>
-    <row r="79" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L79">
         <v>78</v>
       </c>
@@ -8843,27 +9204,27 @@
         <v>8000</v>
       </c>
       <c r="P79">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.2549999999999999</v>
       </c>
       <c r="Q79" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>13.769</v>
       </c>
       <c r="R79">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16400000000000001</v>
       </c>
       <c r="S79" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5208683739455462</v>
       </c>
       <c r="U79">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>13.731999999999999</v>
       </c>
     </row>
-    <row r="80" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L80">
         <v>79</v>
       </c>
@@ -8877,27 +9238,27 @@
         <v>8750</v>
       </c>
       <c r="P80">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>2.339</v>
       </c>
       <c r="Q80" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>14.113</v>
       </c>
       <c r="R80">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.16600000000000001</v>
       </c>
       <c r="S80" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>2.5001858114388091</v>
       </c>
       <c r="U80">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>14.1191</v>
       </c>
     </row>
-    <row r="81" spans="12:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="12:21" x14ac:dyDescent="0.3">
       <c r="L81">
         <v>80</v>
       </c>
@@ -8911,29 +9272,199 @@
         <v>11500</v>
       </c>
       <c r="P81">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
         <v>3.3730000000000002</v>
       </c>
       <c r="Q81" s="4">
-        <f>ROUND(Waves[[#This Row],[Health]]/Waves[[#This Row],[Time]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
         <v>14.502000000000001</v>
       </c>
       <c r="R81">
-        <f>ROUND(Waves[[#This Row],[Money]]/Waves[[#This Row],[Health]],3)</f>
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
         <v>0.23300000000000001</v>
       </c>
       <c r="S81" s="5">
-        <f>Waves[[#This Row],[Money]]/Waves[[#This Row],[Time]]/(SQRT(Waves[[#This Row],[Health]]))*100</f>
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
         <v>3.1455868373806295</v>
       </c>
       <c r="U81">
-        <f>0.0027*Waves[[#This Row],[Wave]]^2-0.0368*Waves[[#This Row],[Wave]]+0.1756</f>
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>14.511600000000001</v>
+      </c>
+    </row>
+    <row r="82" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L82">
+        <v>81</v>
+      </c>
+      <c r="M82">
+        <v>805</v>
+      </c>
+      <c r="N82">
+        <v>1900</v>
+      </c>
+      <c r="O82">
+        <v>12000</v>
+      </c>
+      <c r="P82">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.36</v>
+      </c>
+      <c r="Q82" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>14.907</v>
+      </c>
+      <c r="R82">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.158</v>
+      </c>
+      <c r="S82" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.1546021930845041</v>
+      </c>
+      <c r="U82">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>14.9095</v>
+      </c>
+    </row>
+    <row r="83" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L83">
+        <v>82</v>
+      </c>
+      <c r="M83">
+        <v>455</v>
+      </c>
+      <c r="N83">
+        <v>1100</v>
+      </c>
+      <c r="O83">
+        <v>7000</v>
+      </c>
+      <c r="P83">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.4180000000000001</v>
+      </c>
+      <c r="Q83" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>15.385</v>
+      </c>
+      <c r="R83">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.157</v>
+      </c>
+      <c r="S83" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.8895636709183137</v>
+      </c>
+      <c r="U83">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>15.312800000000001</v>
+      </c>
+    </row>
+    <row r="84" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L84">
+        <v>83</v>
+      </c>
+      <c r="M84">
+        <v>700</v>
+      </c>
+      <c r="N84">
+        <v>1200</v>
+      </c>
+      <c r="O84">
+        <v>11000</v>
+      </c>
+      <c r="P84">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.714</v>
+      </c>
+      <c r="Q84" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>15.714</v>
+      </c>
+      <c r="R84">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.109</v>
+      </c>
+      <c r="S84" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>1.6345072958495868</v>
+      </c>
+      <c r="U84">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>15.721500000000001</v>
+      </c>
+    </row>
+    <row r="85" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L85">
+        <v>84</v>
+      </c>
+      <c r="M85">
+        <v>775</v>
+      </c>
+      <c r="N85">
+        <v>1650</v>
+      </c>
+      <c r="O85">
+        <v>12500</v>
+      </c>
+      <c r="P85">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.129</v>
+      </c>
+      <c r="Q85" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>16.129000000000001</v>
+      </c>
+      <c r="R85">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="S85" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>1.904264342128853</v>
+      </c>
+      <c r="U85">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>16.1356</v>
+      </c>
+    </row>
+    <row r="86" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L86">
+        <v>85</v>
+      </c>
+      <c r="M86">
+        <v>905</v>
+      </c>
+      <c r="N86">
+        <v>2350</v>
+      </c>
+      <c r="O86">
+        <v>15000</v>
+      </c>
+      <c r="P86">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.597</v>
+      </c>
+      <c r="Q86" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>16.574999999999999</v>
+      </c>
+      <c r="R86">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.157</v>
+      </c>
+      <c r="S86" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.1201844919117745</v>
+      </c>
+      <c r="U86">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>16.555099999999999</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="M1:M1048576">
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -8945,7 +9476,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1:P1048576">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -8977,18 +9508,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2611AF0A-4669-45BC-A52D-B98A4F110345}">
   <dimension ref="A1:AJ41"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>6</v>
       </c>
@@ -9032,7 +9563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -9085,7 +9616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -9138,7 +9669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -9191,7 +9722,7 @@
         <v>1.806</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -9244,7 +9775,7 @@
         <v>1.625</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -9297,7 +9828,7 @@
         <v>1.585</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -9358,7 +9889,7 @@
       <c r="AI7" s="7"/>
       <c r="AJ7" s="9"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="L8">
         <v>7</v>
       </c>
@@ -9392,7 +9923,7 @@
       <c r="AI8" s="7"/>
       <c r="AJ8" s="9"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="L9">
         <v>8</v>
       </c>
@@ -9426,7 +9957,7 @@
       <c r="AI9" s="7"/>
       <c r="AJ9" s="9"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="L10">
         <v>9</v>
       </c>
@@ -9460,7 +9991,7 @@
       <c r="AI10" s="7"/>
       <c r="AJ10" s="9"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
@@ -9497,7 +10028,7 @@
       <c r="AI11" s="7"/>
       <c r="AJ11" s="9"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>13</v>
       </c>
@@ -9555,7 +10086,7 @@
       <c r="AI12" s="7"/>
       <c r="AJ12" s="9"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -9616,7 +10147,7 @@
       <c r="AI13" s="7"/>
       <c r="AJ13" s="9"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -9677,7 +10208,7 @@
       <c r="AI14" s="7"/>
       <c r="AJ14" s="9"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>2</v>
       </c>
@@ -9738,7 +10269,7 @@
       <c r="AI15" s="7"/>
       <c r="AJ15" s="9"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -9800,7 +10331,7 @@
       <c r="AI16" s="7"/>
       <c r="AJ16" s="9"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -9853,7 +10384,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -9906,7 +10437,7 @@
         <v>1.238</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L19">
         <v>18</v>
       </c>
@@ -9932,7 +10463,7 @@
         <v>1.321</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L20">
         <v>19</v>
       </c>
@@ -9958,7 +10489,7 @@
         <v>1.145</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L21">
         <v>20</v>
       </c>
@@ -9984,7 +10515,7 @@
         <v>1.127</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L22">
         <v>21</v>
       </c>
@@ -10010,7 +10541,7 @@
         <v>1.083</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L23">
         <v>22</v>
       </c>
@@ -10036,7 +10567,7 @@
         <v>0.96</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L24">
         <v>23</v>
       </c>
@@ -10062,7 +10593,7 @@
         <v>0.97599999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L25">
         <v>24</v>
       </c>
@@ -10088,7 +10619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L26">
         <v>25</v>
       </c>
@@ -10114,7 +10645,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L27">
         <v>26</v>
       </c>
@@ -10140,7 +10671,7 @@
         <v>0.83599999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L28">
         <v>27</v>
       </c>
@@ -10166,7 +10697,7 @@
         <v>0.78800000000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L29">
         <v>28</v>
       </c>
@@ -10192,7 +10723,7 @@
         <v>0.69799999999999995</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L30">
         <v>29</v>
       </c>
@@ -10218,7 +10749,7 @@
         <v>0.76700000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L31">
         <v>30</v>
       </c>
@@ -10244,7 +10775,7 @@
         <v>0.68500000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="L32">
         <v>31</v>
       </c>
@@ -10270,7 +10801,7 @@
         <v>0.623</v>
       </c>
     </row>
-    <row r="33" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L33">
         <v>32</v>
       </c>
@@ -10296,7 +10827,7 @@
         <v>0.65600000000000003</v>
       </c>
     </row>
-    <row r="34" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L34">
         <v>33</v>
       </c>
@@ -10322,7 +10853,7 @@
         <v>0.69699999999999995</v>
       </c>
     </row>
-    <row r="35" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L35">
         <v>34</v>
       </c>
@@ -10348,7 +10879,7 @@
         <v>0.64800000000000002</v>
       </c>
     </row>
-    <row r="36" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L36">
         <v>35</v>
       </c>
@@ -10374,7 +10905,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="37" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L37">
         <v>36</v>
       </c>
@@ -10400,7 +10931,7 @@
         <v>0.35599999999999998</v>
       </c>
     </row>
-    <row r="38" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L38">
         <v>37</v>
       </c>
@@ -10426,7 +10957,7 @@
         <v>0.45900000000000002</v>
       </c>
     </row>
-    <row r="39" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L39">
         <v>38</v>
       </c>
@@ -10452,7 +10983,7 @@
         <v>0.45700000000000002</v>
       </c>
     </row>
-    <row r="40" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L40">
         <v>39</v>
       </c>
@@ -10478,7 +11009,7 @@
         <v>0.38900000000000001</v>
       </c>
     </row>
-    <row r="41" spans="12:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="12:18" x14ac:dyDescent="0.3">
       <c r="L41">
         <v>40</v>
       </c>

--- a/Towers & Upgrades.xlsx
+++ b/Towers & Upgrades.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Daten\Programming\Python\Points TD 2\Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA9792A9-F45E-4A2D-B58D-326E3919926C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{325A1D91-9813-4B45-A2A8-E5DE08EC0BD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,10 +485,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Current!$Q$2:$Q$86</c:f>
+              <c:f>Current!$Q$2:$Q$101</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0.05</c:v>
                 </c:pt>
@@ -743,6 +743,51 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>16.574999999999999</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>16.992999999999999</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>17.417000000000002</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>17.829000000000001</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>18.260999999999999</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>18.727</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>19.108000000000001</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>19.646000000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>20.454999999999998</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>20.859000000000002</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>21.239000000000001</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>22.068999999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>22.43</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>23.231999999999999</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>26.768999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1080,10 +1125,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Current!$P$2:$P$86</c:f>
+              <c:f>Current!$P$2:$P$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>0.14899999999999999</c:v>
                 </c:pt>
@@ -1338,6 +1383,51 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>2.597</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.6339999999999999</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>3.1709999999999998</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2.1709999999999998</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2.9129999999999998</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2.629</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2.9940000000000002</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.8660000000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>3.1160000000000001</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>3.0680000000000001</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.7610000000000001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>3.363</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>3.379</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>3.5510000000000002</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2.8279999999999998</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4.7830000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1381,10 +1471,10 @@
           </c:trendline>
           <c:val>
             <c:numRef>
-              <c:f>Current!$R$2:$R$86</c:f>
+              <c:f>Current!$R$2:$R$101</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>3</c:v>
                 </c:pt>
@@ -1639,6 +1729,51 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>9.6000000000000002E-2</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>0.182</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>0.16</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>0.157</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>9.5000000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>0.156</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>0.15</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>0.13200000000000001</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>0.158</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>0.153</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>0.158</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>0.122</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>0.17899999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1667,10 +1802,10 @@
           </c:marker>
           <c:val>
             <c:numRef>
-              <c:f>Current!$S$2:$S$86</c:f>
+              <c:f>Current!$S$2:$S$101</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="85"/>
+                <c:ptCount val="100"/>
                 <c:pt idx="0">
                   <c:v>2.110766511004619</c:v>
                 </c:pt>
@@ -1925,6 +2060,51 @@
                 </c:pt>
                 <c:pt idx="84">
                   <c:v>2.1201844919117745</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.4331013387369758</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2.8949535272104208</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2.0240414442425414</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2.8428393429370313</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2.6096517544438664</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2.444289127618033</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.8664047151277015</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2.8324567993989485</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2.640670463323239</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2.1173880060203478</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>3.0698314432442935</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2.6715794025560449</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>3.2419715241738802</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2.6373873364372509</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2.6989822294843933</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5351,8 +5531,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D17B983-4C4E-4251-9CC2-79B2CFAB8B8A}" name="Waves4" displayName="Waves4" ref="L1:S86" totalsRowShown="0">
-  <autoFilter ref="L1:S86" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{7D17B983-4C4E-4251-9CC2-79B2CFAB8B8A}" name="Waves4" displayName="Waves4" ref="L1:S101" totalsRowShown="0">
+  <autoFilter ref="L1:S101" xr:uid="{11DBD5DE-DC35-4FD7-B8BD-DDD800B12F15}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{154764AE-2BF6-4E60-A3EE-81C43EB3C9DC}" name="Wave"/>
     <tableColumn id="2" xr3:uid="{8A43BFD4-098B-4841-A8D7-3E1888255D8F}" name="Time"/>
@@ -5660,7 +5840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E183A86B-E41F-4C03-888F-921AD8D0823F}">
-  <dimension ref="A1:U86"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.88671875" customWidth="1"/>
@@ -9460,6 +9640,516 @@
       <c r="U86">
         <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
         <v>16.555099999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L87">
+        <v>86</v>
+      </c>
+      <c r="M87">
+        <v>765</v>
+      </c>
+      <c r="N87">
+        <v>1250</v>
+      </c>
+      <c r="O87">
+        <v>13000</v>
+      </c>
+      <c r="P87">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.6339999999999999</v>
+      </c>
+      <c r="Q87" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>16.992999999999999</v>
+      </c>
+      <c r="R87">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="S87" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>1.4331013387369758</v>
+      </c>
+      <c r="U87">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>16.98</v>
+      </c>
+    </row>
+    <row r="88" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L88">
+        <v>87</v>
+      </c>
+      <c r="M88">
+        <v>689</v>
+      </c>
+      <c r="N88">
+        <v>2185</v>
+      </c>
+      <c r="O88">
+        <v>12000</v>
+      </c>
+      <c r="P88">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.1709999999999998</v>
+      </c>
+      <c r="Q88" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>17.417000000000002</v>
+      </c>
+      <c r="R88">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.182</v>
+      </c>
+      <c r="S88" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.8949535272104208</v>
+      </c>
+      <c r="U88">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>17.410300000000003</v>
+      </c>
+    </row>
+    <row r="89" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L89">
+        <v>88</v>
+      </c>
+      <c r="M89">
+        <v>645</v>
+      </c>
+      <c r="N89">
+        <v>1400</v>
+      </c>
+      <c r="O89">
+        <v>11500</v>
+      </c>
+      <c r="P89">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.1709999999999998</v>
+      </c>
+      <c r="Q89" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>17.829000000000001</v>
+      </c>
+      <c r="R89">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.122</v>
+      </c>
+      <c r="S89" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.0240414442425414</v>
+      </c>
+      <c r="U89">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>17.846</v>
+      </c>
+    </row>
+    <row r="90" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L90">
+        <v>89</v>
+      </c>
+      <c r="M90">
+        <v>575</v>
+      </c>
+      <c r="N90">
+        <v>1675</v>
+      </c>
+      <c r="O90">
+        <v>10500</v>
+      </c>
+      <c r="P90">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.9129999999999998</v>
+      </c>
+      <c r="Q90" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>18.260999999999999</v>
+      </c>
+      <c r="R90">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.16</v>
+      </c>
+      <c r="S90" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.8428393429370313</v>
+      </c>
+      <c r="U90">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>18.287099999999999</v>
+      </c>
+    </row>
+    <row r="91" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L91">
+        <v>90</v>
+      </c>
+      <c r="M91">
+        <v>542</v>
+      </c>
+      <c r="N91">
+        <v>1425</v>
+      </c>
+      <c r="O91">
+        <v>10150</v>
+      </c>
+      <c r="P91">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.629</v>
+      </c>
+      <c r="Q91" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>18.727</v>
+      </c>
+      <c r="R91">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="S91" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.6096517544438664</v>
+      </c>
+      <c r="U91">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>18.733599999999999</v>
+      </c>
+    </row>
+    <row r="92" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L92">
+        <v>91</v>
+      </c>
+      <c r="M92">
+        <v>785</v>
+      </c>
+      <c r="N92">
+        <v>2350</v>
+      </c>
+      <c r="O92">
+        <v>15000</v>
+      </c>
+      <c r="P92">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.9940000000000002</v>
+      </c>
+      <c r="Q92" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>19.108000000000001</v>
+      </c>
+      <c r="R92">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.157</v>
+      </c>
+      <c r="S92" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.444289127618033</v>
+      </c>
+      <c r="U92">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>19.185500000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L93">
+        <v>92</v>
+      </c>
+      <c r="M93">
+        <v>509</v>
+      </c>
+      <c r="N93">
+        <v>950</v>
+      </c>
+      <c r="O93">
+        <v>10000</v>
+      </c>
+      <c r="P93">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="Q93" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>19.646000000000001</v>
+      </c>
+      <c r="R93">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>9.5000000000000001E-2</v>
+      </c>
+      <c r="S93" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>1.8664047151277015</v>
+      </c>
+      <c r="U93">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>19.642800000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L94">
+        <v>93</v>
+      </c>
+      <c r="M94">
+        <v>605</v>
+      </c>
+      <c r="N94">
+        <v>1885</v>
+      </c>
+      <c r="O94">
+        <v>12100</v>
+      </c>
+      <c r="P94">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.1160000000000001</v>
+      </c>
+      <c r="Q94" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>20</v>
+      </c>
+      <c r="R94">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.156</v>
+      </c>
+      <c r="S94" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.8324567993989485</v>
+      </c>
+      <c r="U94">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>20.105499999999999</v>
+      </c>
+    </row>
+    <row r="95" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L95">
+        <v>94</v>
+      </c>
+      <c r="M95">
+        <v>660</v>
+      </c>
+      <c r="N95">
+        <v>2025</v>
+      </c>
+      <c r="O95">
+        <v>13500</v>
+      </c>
+      <c r="P95">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.0680000000000001</v>
+      </c>
+      <c r="Q95" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>20.454999999999998</v>
+      </c>
+      <c r="R95">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.15</v>
+      </c>
+      <c r="S95" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.640670463323239</v>
+      </c>
+      <c r="U95">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>20.573600000000003</v>
+      </c>
+    </row>
+    <row r="96" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L96">
+        <v>95</v>
+      </c>
+      <c r="M96">
+        <v>815</v>
+      </c>
+      <c r="N96">
+        <v>2250</v>
+      </c>
+      <c r="O96">
+        <v>17000</v>
+      </c>
+      <c r="P96">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.7610000000000001</v>
+      </c>
+      <c r="Q96" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>20.859000000000002</v>
+      </c>
+      <c r="R96">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="S96" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.1173880060203478</v>
+      </c>
+      <c r="U96">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>21.0471</v>
+      </c>
+    </row>
+    <row r="97" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L97">
+        <v>96</v>
+      </c>
+      <c r="M97">
+        <v>565</v>
+      </c>
+      <c r="N97">
+        <v>1900</v>
+      </c>
+      <c r="O97">
+        <v>12000</v>
+      </c>
+      <c r="P97">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.363</v>
+      </c>
+      <c r="Q97" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>21.239000000000001</v>
+      </c>
+      <c r="R97">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.158</v>
+      </c>
+      <c r="S97" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.0698314432442935</v>
+      </c>
+      <c r="U97">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>21.526</v>
+      </c>
+    </row>
+    <row r="98" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L98">
+        <v>97</v>
+      </c>
+      <c r="M98">
+        <v>725</v>
+      </c>
+      <c r="N98">
+        <v>2450</v>
+      </c>
+      <c r="O98">
+        <v>16000</v>
+      </c>
+      <c r="P98">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.379</v>
+      </c>
+      <c r="Q98" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>22.068999999999999</v>
+      </c>
+      <c r="R98">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.153</v>
+      </c>
+      <c r="S98" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.6715794025560449</v>
+      </c>
+      <c r="U98">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>22.010300000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L99">
+        <v>98</v>
+      </c>
+      <c r="M99">
+        <v>535</v>
+      </c>
+      <c r="N99">
+        <v>1900</v>
+      </c>
+      <c r="O99">
+        <v>12000</v>
+      </c>
+      <c r="P99">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>3.5510000000000002</v>
+      </c>
+      <c r="Q99" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>22.43</v>
+      </c>
+      <c r="R99">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.158</v>
+      </c>
+      <c r="S99" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>3.2419715241738802</v>
+      </c>
+      <c r="U99">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="100" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L100">
+        <v>99</v>
+      </c>
+      <c r="M100">
+        <v>495</v>
+      </c>
+      <c r="N100">
+        <v>1400</v>
+      </c>
+      <c r="O100">
+        <v>11500</v>
+      </c>
+      <c r="P100">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>2.8279999999999998</v>
+      </c>
+      <c r="Q100" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>23.231999999999999</v>
+      </c>
+      <c r="R100">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.122</v>
+      </c>
+      <c r="S100" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.6373873364372509</v>
+      </c>
+      <c r="U100">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>22.995100000000001</v>
+      </c>
+    </row>
+    <row r="101" spans="12:21" x14ac:dyDescent="0.3">
+      <c r="L101">
+        <v>100</v>
+      </c>
+      <c r="M101">
+        <v>1173</v>
+      </c>
+      <c r="N101">
+        <v>5610</v>
+      </c>
+      <c r="O101">
+        <v>31400</v>
+      </c>
+      <c r="P101">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>4.7830000000000004</v>
+      </c>
+      <c r="Q101" s="4">
+        <f>ROUND(Waves4[[#This Row],[Health]]/Waves4[[#This Row],[Time]],3)</f>
+        <v>26.768999999999998</v>
+      </c>
+      <c r="R101">
+        <f>ROUND(Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Health]],3)</f>
+        <v>0.17899999999999999</v>
+      </c>
+      <c r="S101" s="5">
+        <f>Waves4[[#This Row],[Money]]/Waves4[[#This Row],[Time]]/(SQRT(Waves4[[#This Row],[Health]]))*100</f>
+        <v>2.6989822294843933</v>
+      </c>
+      <c r="U101">
+        <f>0.0027*Waves4[[#This Row],[Wave]]^2-0.0368*Waves4[[#This Row],[Wave]]+0.1756</f>
+        <v>23.4956</v>
       </c>
     </row>
   </sheetData>
